--- a/data/source/weekly/cs-en-us-111pct.xlsx
+++ b/data/source/weekly/cs-en-us-111pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -854,11 +854,11 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="14">
-        <v>1</v>
-      </c>
-      <c r="E14" s="15">
-        <v>-100</v>
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
@@ -895,11 +895,11 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>-100</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="13" t="s">
         <v>20</v>
@@ -964,10 +964,10 @@
         <v>-58.333333333333</v>
       </c>
       <c r="M16" s="15">
-        <v>-61.538461538461</v>
+        <v>-68.75</v>
       </c>
       <c r="N16" s="15">
-        <v>-83.333333333333</v>
+        <v>-85.294117647058</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -977,38 +977,38 @@
       <c r="C17" s="14">
         <v>1</v>
       </c>
-      <c r="D17" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>21</v>
+      <c r="D17" s="14">
+        <v>1</v>
+      </c>
+      <c r="E17" s="15">
+        <v>0</v>
       </c>
       <c r="F17" s="14">
         <v>3</v>
       </c>
       <c r="G17" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H17" s="15">
-        <v>-66.666666666666</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="I17" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J17" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K17" s="15">
-        <v>-64.285714285714</v>
+        <v>-60</v>
       </c>
       <c r="L17" s="15">
-        <v>-54.545454545454</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="M17" s="15">
-        <v>-16.666666666666</v>
+        <v>-25</v>
       </c>
       <c r="N17" s="15">
-        <v>-54.545454545454</v>
+        <v>-64.705882352941</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D18" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F18" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G18" s="14">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H18" s="15">
-        <v>-48</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I18" s="14">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J18" s="14">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K18" s="15">
-        <v>-32.352941176470</v>
+        <v>-27.777777777777</v>
       </c>
       <c r="L18" s="15">
-        <v>-4.166666666666</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="M18" s="15">
-        <v>-30.303030303030</v>
+        <v>-25.714285714285</v>
       </c>
       <c r="N18" s="15">
-        <v>-80.508474576271</v>
+        <v>-80</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D19" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E19" s="15">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F19" s="14">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G19" s="14">
         <v>32</v>
       </c>
       <c r="H19" s="15">
-        <v>28.125</v>
+        <v>31.25</v>
       </c>
       <c r="I19" s="14">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="J19" s="14">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="K19" s="15">
-        <v>35.555555555555</v>
+        <v>36.363636363636</v>
       </c>
       <c r="L19" s="15">
-        <v>27.083333333333</v>
+        <v>33.928571428571</v>
       </c>
       <c r="M19" s="15">
-        <v>29.787234042553</v>
+        <v>38.888888888888</v>
       </c>
       <c r="N19" s="15">
-        <v>12.962962962963</v>
+        <v>27.118644067796</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D20" s="14">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E20" s="15">
-        <v>-14.285714285714</v>
+        <v>400</v>
       </c>
       <c r="F20" s="14">
+        <v>17</v>
+      </c>
+      <c r="G20" s="14">
         <v>14</v>
       </c>
-      <c r="G20" s="14">
-        <v>15</v>
-      </c>
       <c r="H20" s="15">
-        <v>-6.666666666666</v>
+        <v>21.428571428571</v>
       </c>
       <c r="I20" s="14">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J20" s="14">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K20" s="15">
-        <v>-4.166666666666</v>
+        <v>12</v>
       </c>
       <c r="L20" s="15">
-        <v>-20.689655172413</v>
+        <v>-15.151515151515</v>
       </c>
       <c r="M20" s="15">
-        <v>109.090909090909</v>
+        <v>86.666666666666</v>
       </c>
       <c r="N20" s="15">
-        <v>-93.611111111111</v>
+        <v>-93.052109181141</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D21" s="17">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E21" s="18">
-        <v>-9.523809523809</v>
+        <v>64.285714285714</v>
       </c>
       <c r="F21" s="17">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G21" s="17">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H21" s="18">
-        <v>-12.941176470588</v>
+        <v>1.282051282051</v>
       </c>
       <c r="I21" s="17">
-        <v>117</v>
+        <v>140</v>
       </c>
       <c r="J21" s="17">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="K21" s="18">
-        <v>-4.098360655737</v>
+        <v>2.941176470588</v>
       </c>
       <c r="L21" s="18">
-        <v>-6.4</v>
+        <v>-2.097902097902</v>
       </c>
       <c r="M21" s="18">
-        <v>6.363636363636</v>
+        <v>9.375</v>
       </c>
       <c r="N21" s="18">
-        <v>-79.616724738676</v>
+        <v>-78.260869565217</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D24" s="14">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E24" s="15">
-        <v>-38.888888888888</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="F24" s="14">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G24" s="14">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="H24" s="15">
-        <v>-29.787234042553</v>
+        <v>-39.622641509434</v>
       </c>
       <c r="I24" s="14">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="J24" s="14">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="K24" s="15">
-        <v>-5</v>
+        <v>-10.958904109589</v>
       </c>
       <c r="L24" s="15">
-        <v>-22.972972972973</v>
+        <v>-22.619047619047</v>
       </c>
       <c r="M24" s="15">
-        <v>-25</v>
+        <v>-19.753086419753</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1302,14 +1302,14 @@
       <c r="A25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="14">
-        <v>3</v>
+      <c r="C25" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D25" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E25" s="15">
-        <v>-25</v>
+        <v>-100</v>
       </c>
       <c r="F25" s="14">
         <v>4</v>
@@ -1324,13 +1324,13 @@
         <v>4</v>
       </c>
       <c r="J25" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K25" s="15">
-        <v>-55.555555555555</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="L25" s="15">
-        <v>-73.333333333333</v>
+        <v>-76.470588235294</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
+        <v>3</v>
+      </c>
+      <c r="D26" s="14">
         <v>1</v>
       </c>
-      <c r="D26" s="14">
-        <v>2</v>
-      </c>
       <c r="E26" s="15">
-        <v>-50</v>
+        <v>200</v>
       </c>
       <c r="F26" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G26" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H26" s="15">
-        <v>11.111111111111</v>
+        <v>28.571428571428</v>
       </c>
       <c r="I26" s="14">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J26" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K26" s="15">
-        <v>0</v>
+        <v>15.384615384615</v>
       </c>
       <c r="L26" s="15">
-        <v>-29.411764705882</v>
+        <v>-37.5</v>
       </c>
       <c r="M26" s="15">
-        <v>-36.842105263157</v>
+        <v>-25</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,11 +1387,11 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15">
-        <v>-100</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="13" t="s">
         <v>20</v>
@@ -1557,8 +1557,8 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="13" t="s">
-        <v>20</v>
+      <c r="F31" s="14">
+        <v>1</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1566,8 +1566,8 @@
       <c r="H31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I31" s="13" t="s">
-        <v>20</v>
+      <c r="I31" s="14">
+        <v>1</v>
       </c>
       <c r="J31" s="13" t="s">
         <v>20</v>
@@ -1576,7 +1576,7 @@
         <v>21</v>
       </c>
       <c r="L31" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-111pct.xlsx
+++ b/data/source/weekly/cs-en-us-111pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -895,17 +895,17 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>-100</v>
       </c>
       <c r="F15" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" s="15">
         <v>-100</v>
@@ -914,7 +914,7 @@
         <v>20</v>
       </c>
       <c r="J15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K15" s="15">
         <v>-100</v>
@@ -943,13 +943,13 @@
         <v>21</v>
       </c>
       <c r="F16" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G16" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H16" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I16" s="14">
         <v>5</v>
@@ -961,13 +961,13 @@
         <v>66.666666666666</v>
       </c>
       <c r="L16" s="15">
-        <v>-58.333333333333</v>
+        <v>-61.538461538461</v>
       </c>
       <c r="M16" s="15">
-        <v>-68.75</v>
+        <v>-70.588235294117</v>
       </c>
       <c r="N16" s="15">
-        <v>-85.294117647058</v>
+        <v>-87.804878048780</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -977,38 +977,38 @@
       <c r="C17" s="14">
         <v>1</v>
       </c>
-      <c r="D17" s="14">
-        <v>1</v>
-      </c>
-      <c r="E17" s="15">
-        <v>0</v>
+      <c r="D17" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F17" s="14">
         <v>3</v>
       </c>
       <c r="G17" s="14">
+        <v>6</v>
+      </c>
+      <c r="H17" s="15">
+        <v>-50</v>
+      </c>
+      <c r="I17" s="14">
         <v>7</v>
-      </c>
-      <c r="H17" s="15">
-        <v>-57.142857142857</v>
-      </c>
-      <c r="I17" s="14">
-        <v>6</v>
       </c>
       <c r="J17" s="14">
         <v>15</v>
       </c>
       <c r="K17" s="15">
-        <v>-60</v>
+        <v>-53.333333333333</v>
       </c>
       <c r="L17" s="15">
-        <v>-45.454545454545</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="M17" s="15">
-        <v>-25</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="N17" s="15">
-        <v>-64.705882352941</v>
+        <v>-61.111111111111</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D18" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E18" s="15">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F18" s="14">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G18" s="14">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H18" s="15">
-        <v>-33.333333333333</v>
+        <v>-26.086956521739</v>
       </c>
       <c r="I18" s="14">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="J18" s="14">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="K18" s="15">
-        <v>-27.777777777777</v>
+        <v>-22.5</v>
       </c>
       <c r="L18" s="15">
-        <v>-13.333333333333</v>
+        <v>-8.823529411764</v>
       </c>
       <c r="M18" s="15">
-        <v>-25.714285714285</v>
+        <v>-27.906976744186</v>
       </c>
       <c r="N18" s="15">
-        <v>-80</v>
+        <v>-79.870129870129</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D19" s="14">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E19" s="15">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="F19" s="14">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G19" s="14">
         <v>32</v>
       </c>
       <c r="H19" s="15">
-        <v>31.25</v>
+        <v>28.125</v>
       </c>
       <c r="I19" s="14">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="J19" s="14">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="K19" s="15">
-        <v>36.363636363636</v>
+        <v>43.333333333333</v>
       </c>
       <c r="L19" s="15">
-        <v>33.928571428571</v>
+        <v>26.470588235294</v>
       </c>
       <c r="M19" s="15">
-        <v>38.888888888888</v>
+        <v>48.275862068965</v>
       </c>
       <c r="N19" s="15">
-        <v>27.118644067796</v>
+        <v>21.126760563380</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
+        <v>8</v>
+      </c>
+      <c r="D20" s="14">
         <v>5</v>
       </c>
-      <c r="D20" s="14">
-        <v>1</v>
-      </c>
       <c r="E20" s="15">
-        <v>400</v>
+        <v>60</v>
       </c>
       <c r="F20" s="14">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="G20" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H20" s="15">
-        <v>21.428571428571</v>
+        <v>40</v>
       </c>
       <c r="I20" s="14">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="J20" s="14">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="K20" s="15">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="L20" s="15">
-        <v>-15.151515151515</v>
+        <v>-5.263157894736</v>
       </c>
       <c r="M20" s="15">
-        <v>86.666666666666</v>
+        <v>100</v>
       </c>
       <c r="N20" s="15">
-        <v>-93.052109181141</v>
+        <v>-92.122538293216</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,37 +1142,37 @@
         <v>23</v>
       </c>
       <c r="D21" s="17">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E21" s="18">
-        <v>64.285714285714</v>
+        <v>53.333333333333</v>
       </c>
       <c r="F21" s="17">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G21" s="17">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H21" s="18">
-        <v>1.282051282051</v>
+        <v>3.75</v>
       </c>
       <c r="I21" s="17">
-        <v>140</v>
+        <v>165</v>
       </c>
       <c r="J21" s="17">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="K21" s="18">
-        <v>2.941176470588</v>
+        <v>9.271523178807</v>
       </c>
       <c r="L21" s="18">
-        <v>-2.097902097902</v>
+        <v>-1.197604790419</v>
       </c>
       <c r="M21" s="18">
-        <v>9.375</v>
+        <v>12.244897959183</v>
       </c>
       <c r="N21" s="18">
-        <v>-78.260869565217</v>
+        <v>-77.762803234501</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D24" s="14">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E24" s="15">
-        <v>-38.461538461538</v>
+        <v>-25</v>
       </c>
       <c r="F24" s="14">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="G24" s="14">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="H24" s="15">
-        <v>-39.622641509434</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="I24" s="14">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J24" s="14">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="K24" s="15">
-        <v>-10.958904109589</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="L24" s="15">
-        <v>-22.619047619047</v>
+        <v>-31.25</v>
       </c>
       <c r="M24" s="15">
-        <v>-19.753086419753</v>
+        <v>-25</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1305,20 +1305,20 @@
       <c r="C25" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D25" s="14">
-        <v>2</v>
-      </c>
-      <c r="E25" s="15">
-        <v>-100</v>
+      <c r="D25" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E25" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F25" s="14">
         <v>4</v>
       </c>
       <c r="G25" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H25" s="15">
-        <v>-55.555555555555</v>
+        <v>-50</v>
       </c>
       <c r="I25" s="14">
         <v>4</v>
@@ -1343,23 +1343,23 @@
       <c r="A26" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="C26" s="14">
-        <v>3</v>
-      </c>
-      <c r="D26" s="14">
-        <v>1</v>
-      </c>
-      <c r="E26" s="15">
-        <v>200</v>
+      <c r="C26" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D26" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E26" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F26" s="14">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G26" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H26" s="15">
-        <v>28.571428571428</v>
+        <v>20</v>
       </c>
       <c r="I26" s="14">
         <v>15</v>
@@ -1371,10 +1371,10 @@
         <v>15.384615384615</v>
       </c>
       <c r="L26" s="15">
-        <v>-37.5</v>
+        <v>-42.307692307692</v>
       </c>
       <c r="M26" s="15">
-        <v>-25</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,11 +1387,11 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>-100</v>
       </c>
       <c r="F27" s="13" t="s">
         <v>20</v>
@@ -1406,7 +1406,7 @@
         <v>20</v>
       </c>
       <c r="J27" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K27" s="15">
         <v>-100</v>

--- a/data/source/weekly/cs-en-us-111pct.xlsx
+++ b/data/source/weekly/cs-en-us-111pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -895,11 +895,11 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>-100</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="13" t="s">
         <v>20</v>
@@ -925,8 +925,8 @@
       <c r="M15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="N15" s="13" t="s">
-        <v>21</v>
+      <c r="N15" s="15">
+        <v>-100</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -942,14 +942,14 @@
       <c r="E16" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F16" s="14">
-        <v>1</v>
-      </c>
-      <c r="G16" s="14">
-        <v>1</v>
-      </c>
-      <c r="H16" s="15">
-        <v>0</v>
+      <c r="F16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H16" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I16" s="14">
         <v>5</v>
@@ -961,13 +961,13 @@
         <v>66.666666666666</v>
       </c>
       <c r="L16" s="15">
-        <v>-61.538461538461</v>
+        <v>-64.285714285714</v>
       </c>
       <c r="M16" s="15">
         <v>-70.588235294117</v>
       </c>
       <c r="N16" s="15">
-        <v>-87.804878048780</v>
+        <v>-90.909090909090</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
+        <v>2</v>
+      </c>
+      <c r="D17" s="14">
         <v>1</v>
       </c>
-      <c r="D17" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>21</v>
+      <c r="E17" s="15">
+        <v>100</v>
       </c>
       <c r="F17" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G17" s="14">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H17" s="15">
-        <v>-50</v>
+        <v>150</v>
       </c>
       <c r="I17" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J17" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K17" s="15">
-        <v>-53.333333333333</v>
+        <v>-43.75</v>
       </c>
       <c r="L17" s="15">
-        <v>-41.666666666666</v>
+        <v>-25</v>
       </c>
       <c r="M17" s="15">
-        <v>-36.363636363636</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="N17" s="15">
-        <v>-61.111111111111</v>
+        <v>-59.090909090909</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D18" s="14">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E18" s="15">
-        <v>25</v>
+        <v>-50</v>
       </c>
       <c r="F18" s="14">
         <v>17</v>
       </c>
       <c r="G18" s="14">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="H18" s="15">
-        <v>-26.086956521739</v>
+        <v>-10.526315789473</v>
       </c>
       <c r="I18" s="14">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J18" s="14">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="K18" s="15">
-        <v>-22.5</v>
+        <v>-27.083333333333</v>
       </c>
       <c r="L18" s="15">
-        <v>-8.823529411764</v>
+        <v>-12.5</v>
       </c>
       <c r="M18" s="15">
-        <v>-27.906976744186</v>
+        <v>-31.372549019607</v>
       </c>
       <c r="N18" s="15">
-        <v>-79.870129870129</v>
+        <v>-78.787878787878</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,13 +1057,13 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D19" s="14">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E19" s="15">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="F19" s="14">
         <v>41</v>
@@ -1075,22 +1075,22 @@
         <v>28.125</v>
       </c>
       <c r="I19" s="14">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="J19" s="14">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="K19" s="15">
-        <v>43.333333333333</v>
+        <v>38.571428571428</v>
       </c>
       <c r="L19" s="15">
-        <v>26.470588235294</v>
+        <v>25.974025974026</v>
       </c>
       <c r="M19" s="15">
-        <v>48.275862068965</v>
+        <v>56.451612903225</v>
       </c>
       <c r="N19" s="15">
-        <v>21.126760563380</v>
+        <v>24.358974358974</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D20" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E20" s="15">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="F20" s="14">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G20" s="14">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H20" s="15">
-        <v>40</v>
+        <v>31.578947368421</v>
       </c>
       <c r="I20" s="14">
+        <v>42</v>
+      </c>
+      <c r="J20" s="14">
         <v>36</v>
       </c>
-      <c r="J20" s="14">
-        <v>30</v>
-      </c>
       <c r="K20" s="15">
-        <v>20</v>
+        <v>16.666666666666</v>
       </c>
       <c r="L20" s="15">
-        <v>-5.263157894736</v>
+        <v>-4.545454545454</v>
       </c>
       <c r="M20" s="15">
-        <v>100</v>
+        <v>121.052631578947</v>
       </c>
       <c r="N20" s="15">
-        <v>-92.122538293216</v>
+        <v>-91.954022988505</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,37 +1142,37 @@
         <v>23</v>
       </c>
       <c r="D21" s="17">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="E21" s="18">
-        <v>53.333333333333</v>
+        <v>-8</v>
       </c>
       <c r="F21" s="17">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="G21" s="17">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H21" s="18">
-        <v>3.75</v>
+        <v>17.333333333333</v>
       </c>
       <c r="I21" s="17">
-        <v>165</v>
+        <v>188</v>
       </c>
       <c r="J21" s="17">
-        <v>151</v>
+        <v>176</v>
       </c>
       <c r="K21" s="18">
-        <v>9.271523178807</v>
+        <v>6.818181818181</v>
       </c>
       <c r="L21" s="18">
-        <v>-1.197604790419</v>
+        <v>-1.052631578947</v>
       </c>
       <c r="M21" s="18">
-        <v>12.244897959183</v>
+        <v>17.5</v>
       </c>
       <c r="N21" s="18">
-        <v>-77.762803234501</v>
+        <v>-77.725118483412</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D24" s="14">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E24" s="15">
-        <v>-25</v>
+        <v>-37.5</v>
       </c>
       <c r="F24" s="14">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G24" s="14">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="H24" s="15">
-        <v>-41.666666666666</v>
+        <v>-37.209302325581</v>
       </c>
       <c r="I24" s="14">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="J24" s="14">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="K24" s="15">
-        <v>-14.285714285714</v>
+        <v>-16.470588235294</v>
       </c>
       <c r="L24" s="15">
-        <v>-31.25</v>
+        <v>-33.018867924528</v>
       </c>
       <c r="M24" s="15">
-        <v>-25</v>
+        <v>-21.111111111111</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1312,10 +1312,10 @@
         <v>21</v>
       </c>
       <c r="F25" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G25" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H25" s="15">
         <v>-50</v>
@@ -1330,7 +1330,7 @@
         <v>-63.636363636363</v>
       </c>
       <c r="L25" s="15">
-        <v>-76.470588235294</v>
+        <v>-80.952380952380</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1343,38 +1343,38 @@
       <c r="A26" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="C26" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D26" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E26" s="13" t="s">
-        <v>21</v>
+      <c r="C26" s="14">
+        <v>3</v>
+      </c>
+      <c r="D26" s="14">
+        <v>3</v>
+      </c>
+      <c r="E26" s="15">
+        <v>0</v>
       </c>
       <c r="F26" s="14">
+        <v>7</v>
+      </c>
+      <c r="G26" s="14">
         <v>6</v>
       </c>
-      <c r="G26" s="14">
-        <v>5</v>
-      </c>
       <c r="H26" s="15">
-        <v>20</v>
+        <v>16.666666666666</v>
       </c>
       <c r="I26" s="14">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J26" s="14">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K26" s="15">
-        <v>15.384615384615</v>
+        <v>12.5</v>
       </c>
       <c r="L26" s="15">
-        <v>-42.307692307692</v>
+        <v>-40</v>
       </c>
       <c r="M26" s="15">
-        <v>-28.571428571428</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,11 +1387,11 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15">
-        <v>-100</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="13" t="s">
         <v>20</v>
@@ -1551,29 +1551,29 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="14">
+        <v>1</v>
+      </c>
+      <c r="E31" s="15">
+        <v>-100</v>
       </c>
       <c r="F31" s="14">
         <v>1</v>
       </c>
-      <c r="G31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>21</v>
+      <c r="G31" s="14">
+        <v>1</v>
+      </c>
+      <c r="H31" s="15">
+        <v>0</v>
       </c>
       <c r="I31" s="14">
         <v>1</v>
       </c>
-      <c r="J31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K31" s="13" t="s">
-        <v>21</v>
+      <c r="J31" s="14">
+        <v>1</v>
+      </c>
+      <c r="K31" s="15">
+        <v>0</v>
       </c>
       <c r="L31" s="15">
         <v>0</v>

--- a/data/source/weekly/cs-en-us-111pct.xlsx
+++ b/data/source/weekly/cs-en-us-111pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -863,11 +863,11 @@
       <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="14">
-        <v>1</v>
-      </c>
-      <c r="H14" s="15">
-        <v>-100</v>
+      <c r="G14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I14" s="13" t="s">
         <v>20</v>
@@ -905,7 +905,7 @@
         <v>20</v>
       </c>
       <c r="G15" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H15" s="15">
         <v>-100</v>
@@ -922,8 +922,8 @@
       <c r="L15" s="15">
         <v>-100</v>
       </c>
-      <c r="M15" s="13" t="s">
-        <v>21</v>
+      <c r="M15" s="15">
+        <v>-100</v>
       </c>
       <c r="N15" s="15">
         <v>-100</v>
@@ -936,38 +936,38 @@
       <c r="C16" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
+      <c r="D16" s="14">
+        <v>1</v>
+      </c>
+      <c r="E16" s="15">
+        <v>-100</v>
       </c>
       <c r="F16" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H16" s="13" t="s">
-        <v>21</v>
+      <c r="G16" s="14">
+        <v>1</v>
+      </c>
+      <c r="H16" s="15">
+        <v>-100</v>
       </c>
       <c r="I16" s="14">
         <v>5</v>
       </c>
       <c r="J16" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K16" s="15">
-        <v>66.666666666666</v>
+        <v>25</v>
       </c>
       <c r="L16" s="15">
-        <v>-64.285714285714</v>
+        <v>-68.75</v>
       </c>
       <c r="M16" s="15">
-        <v>-70.588235294117</v>
+        <v>-72.222222222222</v>
       </c>
       <c r="N16" s="15">
-        <v>-90.909090909090</v>
+        <v>-92.424242424242</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
+        <v>1</v>
+      </c>
+      <c r="D17" s="14">
         <v>2</v>
       </c>
-      <c r="D17" s="14">
-        <v>1</v>
-      </c>
       <c r="E17" s="15">
-        <v>100</v>
+        <v>-50</v>
       </c>
       <c r="F17" s="14">
         <v>5</v>
       </c>
       <c r="G17" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H17" s="15">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="I17" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J17" s="14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K17" s="15">
-        <v>-43.75</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="L17" s="15">
-        <v>-25</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="M17" s="15">
-        <v>-18.181818181818</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="N17" s="15">
-        <v>-59.090909090909</v>
+        <v>-56.521739130434</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="F18" s="14">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G18" s="14">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H18" s="15">
-        <v>-10.526315789473</v>
+        <v>-12.5</v>
       </c>
       <c r="I18" s="14">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J18" s="14">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="K18" s="15">
-        <v>-27.083333333333</v>
+        <v>-26</v>
       </c>
       <c r="L18" s="15">
-        <v>-12.5</v>
+        <v>-19.565217391304</v>
       </c>
       <c r="M18" s="15">
-        <v>-31.372549019607</v>
+        <v>-33.928571428571</v>
       </c>
       <c r="N18" s="15">
-        <v>-78.787878787878</v>
+        <v>-80.319148936170</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D19" s="14">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E19" s="15">
-        <v>10</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="F19" s="14">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="G19" s="14">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="H19" s="15">
-        <v>28.125</v>
+        <v>17.5</v>
       </c>
       <c r="I19" s="14">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="J19" s="14">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="K19" s="15">
-        <v>38.571428571428</v>
+        <v>30.588235294117</v>
       </c>
       <c r="L19" s="15">
-        <v>25.974025974026</v>
+        <v>27.586206896551</v>
       </c>
       <c r="M19" s="15">
-        <v>56.451612903225</v>
+        <v>56.338028169014</v>
       </c>
       <c r="N19" s="15">
-        <v>24.358974358974</v>
+        <v>19.354838709677</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D20" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E20" s="15">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F20" s="14">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="G20" s="14">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H20" s="15">
-        <v>31.578947368421</v>
+        <v>47.619047619047</v>
       </c>
       <c r="I20" s="14">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="J20" s="14">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="K20" s="15">
-        <v>16.666666666666</v>
+        <v>20</v>
       </c>
       <c r="L20" s="15">
-        <v>-4.545454545454</v>
+        <v>3.846153846153</v>
       </c>
       <c r="M20" s="15">
-        <v>121.052631578947</v>
+        <v>125</v>
       </c>
       <c r="N20" s="15">
-        <v>-91.954022988505</v>
+        <v>-90.689655172413</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D21" s="17">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E21" s="18">
-        <v>-8</v>
+        <v>-3.448275862068</v>
       </c>
       <c r="F21" s="17">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="G21" s="17">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H21" s="18">
-        <v>17.333333333333</v>
+        <v>16.867469879518</v>
       </c>
       <c r="I21" s="17">
-        <v>188</v>
+        <v>217</v>
       </c>
       <c r="J21" s="17">
-        <v>176</v>
+        <v>205</v>
       </c>
       <c r="K21" s="18">
-        <v>6.818181818181</v>
+        <v>5.853658536585</v>
       </c>
       <c r="L21" s="18">
-        <v>-1.052631578947</v>
+        <v>-0.458715596330</v>
       </c>
       <c r="M21" s="18">
-        <v>17.5</v>
+        <v>19.889502762430</v>
       </c>
       <c r="N21" s="18">
-        <v>-77.725118483412</v>
+        <v>-77.205882352941</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D24" s="14">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E24" s="15">
-        <v>-37.5</v>
+        <v>-25</v>
       </c>
       <c r="F24" s="14">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G24" s="14">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="H24" s="15">
-        <v>-37.209302325581</v>
+        <v>-32.432432432432</v>
       </c>
       <c r="I24" s="14">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="J24" s="14">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="K24" s="15">
-        <v>-16.470588235294</v>
+        <v>-18.556701030927</v>
       </c>
       <c r="L24" s="15">
-        <v>-33.018867924528</v>
+        <v>-30.088495575221</v>
       </c>
       <c r="M24" s="15">
-        <v>-21.111111111111</v>
+        <v>-20.202020202020</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1302,35 +1302,35 @@
       <c r="A25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D25" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E25" s="13" t="s">
-        <v>21</v>
+      <c r="C25" s="14">
+        <v>1</v>
+      </c>
+      <c r="D25" s="14">
+        <v>2</v>
+      </c>
+      <c r="E25" s="15">
+        <v>-50</v>
       </c>
       <c r="F25" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G25" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H25" s="15">
-        <v>-50</v>
+        <v>-75</v>
       </c>
       <c r="I25" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J25" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K25" s="15">
-        <v>-63.636363636363</v>
+        <v>-61.538461538461</v>
       </c>
       <c r="L25" s="15">
-        <v>-80.952380952380</v>
+        <v>-77.272727272727</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,34 +1347,34 @@
         <v>3</v>
       </c>
       <c r="D26" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E26" s="15">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F26" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G26" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H26" s="15">
-        <v>16.666666666666</v>
+        <v>80</v>
       </c>
       <c r="I26" s="14">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J26" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K26" s="15">
-        <v>12.5</v>
+        <v>23.529411764705</v>
       </c>
       <c r="L26" s="15">
-        <v>-40</v>
+        <v>-32.258064516129</v>
       </c>
       <c r="M26" s="15">
-        <v>-14.285714285714</v>
+        <v>-19.230769230769</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1397,7 +1397,7 @@
         <v>20</v>
       </c>
       <c r="G27" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H27" s="15">
         <v>-100</v>
@@ -1425,8 +1425,8 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="14">
+        <v>1</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>20</v>
@@ -1434,8 +1434,8 @@
       <c r="E28" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F28" s="13" t="s">
-        <v>20</v>
+      <c r="F28" s="14">
+        <v>1</v>
       </c>
       <c r="G28" s="13" t="s">
         <v>20</v>
@@ -1443,8 +1443,8 @@
       <c r="H28" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I28" s="13" t="s">
-        <v>20</v>
+      <c r="I28" s="14">
+        <v>1</v>
       </c>
       <c r="J28" s="13" t="s">
         <v>20</v>
@@ -1453,7 +1453,7 @@
         <v>21</v>
       </c>
       <c r="L28" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1557,23 +1557,23 @@
       <c r="E31" s="15">
         <v>-100</v>
       </c>
-      <c r="F31" s="14">
-        <v>1</v>
+      <c r="F31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G31" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H31" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I31" s="14">
         <v>1</v>
       </c>
       <c r="J31" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K31" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="L31" s="15">
         <v>0</v>

--- a/data/source/weekly/cs-en-us-111pct.xlsx
+++ b/data/source/weekly/cs-en-us-111pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -901,32 +901,32 @@
       <c r="E15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F15" s="13" t="s">
-        <v>20</v>
+      <c r="F15" s="14">
+        <v>1</v>
       </c>
       <c r="G15" s="14">
         <v>1</v>
       </c>
       <c r="H15" s="15">
-        <v>-100</v>
-      </c>
-      <c r="I15" s="13" t="s">
-        <v>20</v>
+        <v>0</v>
+      </c>
+      <c r="I15" s="14">
+        <v>1</v>
       </c>
       <c r="J15" s="14">
         <v>2</v>
       </c>
       <c r="K15" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="L15" s="15">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M15" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="N15" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -936,11 +936,11 @@
       <c r="C16" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D16" s="14">
-        <v>1</v>
-      </c>
-      <c r="E16" s="15">
-        <v>-100</v>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F16" s="13" t="s">
         <v>20</v>
@@ -967,7 +967,7 @@
         <v>-72.222222222222</v>
       </c>
       <c r="N16" s="15">
-        <v>-92.424242424242</v>
+        <v>-93.243243243243</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E17" s="15">
+        <v>-33.333333333333</v>
+      </c>
+      <c r="F17" s="14">
+        <v>6</v>
+      </c>
+      <c r="G17" s="14">
+        <v>6</v>
+      </c>
+      <c r="H17" s="15">
+        <v>0</v>
+      </c>
+      <c r="I17" s="14">
+        <v>12</v>
+      </c>
+      <c r="J17" s="14">
+        <v>21</v>
+      </c>
+      <c r="K17" s="15">
+        <v>-42.857142857142</v>
+      </c>
+      <c r="L17" s="15">
+        <v>-33.333333333333</v>
+      </c>
+      <c r="M17" s="15">
+        <v>9.090909090909</v>
+      </c>
+      <c r="N17" s="15">
         <v>-50</v>
-      </c>
-      <c r="F17" s="14">
-        <v>5</v>
-      </c>
-      <c r="G17" s="14">
-        <v>4</v>
-      </c>
-      <c r="H17" s="15">
-        <v>25</v>
-      </c>
-      <c r="I17" s="14">
-        <v>10</v>
-      </c>
-      <c r="J17" s="14">
-        <v>18</v>
-      </c>
-      <c r="K17" s="15">
-        <v>-44.444444444444</v>
-      </c>
-      <c r="L17" s="15">
-        <v>-28.571428571428</v>
-      </c>
-      <c r="M17" s="15">
-        <v>-9.090909090909</v>
-      </c>
-      <c r="N17" s="15">
-        <v>-56.521739130434</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D18" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E18" s="15">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="F18" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G18" s="14">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H18" s="15">
-        <v>-12.5</v>
+        <v>-21.052631578947</v>
       </c>
       <c r="I18" s="14">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="J18" s="14">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="K18" s="15">
-        <v>-26</v>
+        <v>-25.454545454545</v>
       </c>
       <c r="L18" s="15">
-        <v>-19.565217391304</v>
+        <v>-19.607843137254</v>
       </c>
       <c r="M18" s="15">
-        <v>-33.928571428571</v>
+        <v>-31.666666666666</v>
       </c>
       <c r="N18" s="15">
-        <v>-80.319148936170</v>
+        <v>-80.097087378640</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,37 +1060,37 @@
         <v>13</v>
       </c>
       <c r="D19" s="14">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E19" s="15">
-        <v>-13.333333333333</v>
+        <v>62.5</v>
       </c>
       <c r="F19" s="14">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G19" s="14">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H19" s="15">
-        <v>17.5</v>
+        <v>21.052631578947</v>
       </c>
       <c r="I19" s="14">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="J19" s="14">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="K19" s="15">
-        <v>30.588235294117</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L19" s="15">
-        <v>27.586206896551</v>
+        <v>31.914893617021</v>
       </c>
       <c r="M19" s="15">
-        <v>56.338028169014</v>
+        <v>55</v>
       </c>
       <c r="N19" s="15">
-        <v>19.354838709677</v>
+        <v>22.772277227722</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D20" s="14">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E20" s="15">
-        <v>33.333333333333</v>
+        <v>800</v>
       </c>
       <c r="F20" s="14">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G20" s="14">
         <v>21</v>
       </c>
       <c r="H20" s="15">
-        <v>47.619047619047</v>
+        <v>66.666666666666</v>
       </c>
       <c r="I20" s="14">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="J20" s="14">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K20" s="15">
-        <v>20</v>
+        <v>36.956521739130</v>
       </c>
       <c r="L20" s="15">
-        <v>3.846153846153</v>
+        <v>10.526315789473</v>
       </c>
       <c r="M20" s="15">
-        <v>125</v>
+        <v>142.307692307692</v>
       </c>
       <c r="N20" s="15">
-        <v>-90.689655172413</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D21" s="17">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="E21" s="18">
-        <v>-3.448275862068</v>
+        <v>70.588235294117</v>
       </c>
       <c r="F21" s="17">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="G21" s="17">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="H21" s="18">
-        <v>16.867469879518</v>
+        <v>19.767441860465</v>
       </c>
       <c r="I21" s="17">
-        <v>217</v>
+        <v>246</v>
       </c>
       <c r="J21" s="17">
-        <v>205</v>
+        <v>222</v>
       </c>
       <c r="K21" s="18">
-        <v>5.853658536585</v>
+        <v>10.810810810810</v>
       </c>
       <c r="L21" s="18">
-        <v>-0.458715596330</v>
+        <v>2.928870292887</v>
       </c>
       <c r="M21" s="18">
-        <v>19.889502762430</v>
+        <v>25.510204081632</v>
       </c>
       <c r="N21" s="18">
-        <v>-77.205882352941</v>
+        <v>-76.277724204435</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D24" s="14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E24" s="15">
-        <v>-25</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="F24" s="14">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G24" s="14">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H24" s="15">
-        <v>-32.432432432432</v>
+        <v>-37.142857142857</v>
       </c>
       <c r="I24" s="14">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="J24" s="14">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="K24" s="15">
-        <v>-18.556701030927</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="L24" s="15">
-        <v>-30.088495575221</v>
+        <v>-27.586206896551</v>
       </c>
       <c r="M24" s="15">
-        <v>-20.202020202020</v>
+        <v>-18.446601941747</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,31 +1306,31 @@
         <v>1</v>
       </c>
       <c r="D25" s="14">
+        <v>5</v>
+      </c>
+      <c r="E25" s="15">
+        <v>-80</v>
+      </c>
+      <c r="F25" s="14">
         <v>2</v>
       </c>
-      <c r="E25" s="15">
-        <v>-50</v>
-      </c>
-      <c r="F25" s="14">
-        <v>1</v>
-      </c>
       <c r="G25" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H25" s="15">
-        <v>-75</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="I25" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J25" s="14">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K25" s="15">
-        <v>-61.538461538461</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L25" s="15">
-        <v>-77.272727272727</v>
+        <v>-72.727272727272</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,34 +1347,34 @@
         <v>3</v>
       </c>
       <c r="D26" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E26" s="15">
-        <v>200</v>
+        <v>-25</v>
       </c>
       <c r="F26" s="14">
         <v>9</v>
       </c>
       <c r="G26" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H26" s="15">
-        <v>80</v>
+        <v>12.5</v>
       </c>
       <c r="I26" s="14">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J26" s="14">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="K26" s="15">
-        <v>23.529411764705</v>
+        <v>14.285714285714</v>
       </c>
       <c r="L26" s="15">
-        <v>-32.258064516129</v>
+        <v>-31.428571428571</v>
       </c>
       <c r="M26" s="15">
-        <v>-19.230769230769</v>
+        <v>-17.241379310344</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>2</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1393,26 +1393,26 @@
       <c r="E27" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F27" s="13" t="s">
-        <v>20</v>
+      <c r="F27" s="14">
+        <v>2</v>
       </c>
       <c r="G27" s="14">
         <v>1</v>
       </c>
       <c r="H27" s="15">
-        <v>-100</v>
-      </c>
-      <c r="I27" s="13" t="s">
-        <v>20</v>
+        <v>100</v>
+      </c>
+      <c r="I27" s="14">
+        <v>2</v>
       </c>
       <c r="J27" s="14">
         <v>3</v>
       </c>
       <c r="K27" s="15">
-        <v>-100</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L27" s="15">
-        <v>-100</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,8 +1425,8 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>1</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>20</v>
@@ -1551,11 +1551,11 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="14">
-        <v>1</v>
-      </c>
-      <c r="E31" s="15">
-        <v>-100</v>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-111pct.xlsx
+++ b/data/source/weekly/cs-en-us-111pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>1</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -904,11 +904,11 @@
       <c r="F15" s="14">
         <v>1</v>
       </c>
-      <c r="G15" s="14">
-        <v>1</v>
-      </c>
-      <c r="H15" s="15">
-        <v>0</v>
+      <c r="G15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I15" s="14">
         <v>1</v>
@@ -926,48 +926,48 @@
         <v>0</v>
       </c>
       <c r="N15" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F16" s="13" t="s">
-        <v>20</v>
+      <c r="C16" s="14">
+        <v>2</v>
+      </c>
+      <c r="D16" s="14">
+        <v>1</v>
+      </c>
+      <c r="E16" s="15">
+        <v>100</v>
+      </c>
+      <c r="F16" s="14">
+        <v>2</v>
       </c>
       <c r="G16" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H16" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I16" s="14">
+        <v>7</v>
+      </c>
+      <c r="J16" s="14">
         <v>5</v>
       </c>
-      <c r="J16" s="14">
-        <v>4</v>
-      </c>
       <c r="K16" s="15">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="L16" s="15">
-        <v>-68.75</v>
+        <v>-58.823529411764</v>
       </c>
       <c r="M16" s="15">
-        <v>-72.222222222222</v>
+        <v>-68.181818181818</v>
       </c>
       <c r="N16" s="15">
-        <v>-93.243243243243</v>
+        <v>-91.954022988505</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,37 +978,37 @@
         <v>2</v>
       </c>
       <c r="D17" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E17" s="15">
-        <v>-33.333333333333</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F17" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G17" s="14">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H17" s="15">
-        <v>0</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="I17" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J17" s="14">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="K17" s="15">
-        <v>-42.857142857142</v>
+        <v>-48.148148148148</v>
       </c>
       <c r="L17" s="15">
-        <v>-33.333333333333</v>
+        <v>-26.315789473684</v>
       </c>
       <c r="M17" s="15">
-        <v>9.090909090909</v>
+        <v>16.666666666666</v>
       </c>
       <c r="N17" s="15">
-        <v>-50</v>
+        <v>-46.153846153846</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D18" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E18" s="15">
-        <v>-20</v>
+        <v>-50</v>
       </c>
       <c r="F18" s="14">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G18" s="14">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H18" s="15">
-        <v>-21.052631578947</v>
+        <v>-38.095238095238</v>
       </c>
       <c r="I18" s="14">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J18" s="14">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="K18" s="15">
-        <v>-25.454545454545</v>
+        <v>-27.868852459016</v>
       </c>
       <c r="L18" s="15">
-        <v>-19.607843137254</v>
+        <v>-16.981132075471</v>
       </c>
       <c r="M18" s="15">
-        <v>-31.666666666666</v>
+        <v>-29.032258064516</v>
       </c>
       <c r="N18" s="15">
-        <v>-80.097087378640</v>
+        <v>-80.090497737556</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D19" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E19" s="15">
-        <v>62.5</v>
+        <v>60</v>
       </c>
       <c r="F19" s="14">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G19" s="14">
         <v>38</v>
       </c>
       <c r="H19" s="15">
-        <v>21.052631578947</v>
+        <v>18.421052631578</v>
       </c>
       <c r="I19" s="14">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="J19" s="14">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="K19" s="15">
-        <v>33.333333333333</v>
+        <v>36.734693877551</v>
       </c>
       <c r="L19" s="15">
-        <v>31.914893617021</v>
+        <v>27.619047619047</v>
       </c>
       <c r="M19" s="15">
-        <v>55</v>
+        <v>52.272727272727</v>
       </c>
       <c r="N19" s="15">
-        <v>22.772277227722</v>
+        <v>15.517241379310</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D20" s="14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E20" s="15">
-        <v>800</v>
+        <v>40</v>
       </c>
       <c r="F20" s="14">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G20" s="14">
         <v>21</v>
       </c>
       <c r="H20" s="15">
-        <v>66.666666666666</v>
+        <v>61.904761904761</v>
       </c>
       <c r="I20" s="14">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="J20" s="14">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="K20" s="15">
-        <v>36.956521739130</v>
+        <v>37.254901960784</v>
       </c>
       <c r="L20" s="15">
-        <v>10.526315789473</v>
+        <v>16.666666666666</v>
       </c>
       <c r="M20" s="15">
-        <v>142.307692307692</v>
+        <v>150</v>
       </c>
       <c r="N20" s="15">
-        <v>-90</v>
+        <v>-89.928057553956</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D21" s="17">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E21" s="18">
-        <v>70.588235294117</v>
+        <v>-4.347826086956</v>
       </c>
       <c r="F21" s="17">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G21" s="17">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="H21" s="18">
-        <v>19.767441860465</v>
+        <v>8.510638297872</v>
       </c>
       <c r="I21" s="17">
-        <v>246</v>
+        <v>270</v>
       </c>
       <c r="J21" s="17">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="K21" s="18">
-        <v>10.810810810810</v>
+        <v>10.204081632653</v>
       </c>
       <c r="L21" s="18">
-        <v>2.928870292887</v>
+        <v>5.058365758754</v>
       </c>
       <c r="M21" s="18">
-        <v>25.510204081632</v>
+        <v>26.760563380281</v>
       </c>
       <c r="N21" s="18">
-        <v>-76.277724204435</v>
+        <v>-76.480836236933</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D24" s="14">
         <v>11</v>
       </c>
       <c r="E24" s="15">
-        <v>-45.454545454545</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="F24" s="14">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="G24" s="14">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="H24" s="15">
-        <v>-37.142857142857</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I24" s="14">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="J24" s="14">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="K24" s="15">
-        <v>-22.222222222222</v>
+        <v>-23.529411764705</v>
       </c>
       <c r="L24" s="15">
-        <v>-27.586206896551</v>
+        <v>-31.060606060606</v>
       </c>
       <c r="M24" s="15">
-        <v>-18.446601941747</v>
+        <v>-19.469026548672</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1302,35 +1302,35 @@
       <c r="A25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="14">
+      <c r="C25" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D25" s="14">
         <v>1</v>
       </c>
-      <c r="D25" s="14">
-        <v>5</v>
-      </c>
       <c r="E25" s="15">
-        <v>-80</v>
+        <v>-100</v>
       </c>
       <c r="F25" s="14">
         <v>2</v>
       </c>
       <c r="G25" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H25" s="15">
-        <v>-71.428571428571</v>
+        <v>-75</v>
       </c>
       <c r="I25" s="14">
         <v>6</v>
       </c>
       <c r="J25" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K25" s="15">
-        <v>-66.666666666666</v>
+        <v>-68.421052631578</v>
       </c>
       <c r="L25" s="15">
-        <v>-72.727272727272</v>
+        <v>-76.923076923076</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D26" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E26" s="15">
-        <v>-25</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="F26" s="14">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G26" s="14">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="H26" s="15">
-        <v>12.5</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="I26" s="14">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J26" s="14">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="K26" s="15">
-        <v>14.285714285714</v>
+        <v>0</v>
       </c>
       <c r="L26" s="15">
-        <v>-31.428571428571</v>
+        <v>-30</v>
       </c>
       <c r="M26" s="15">
-        <v>-17.241379310344</v>
+        <v>-9.677419354838</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>2</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1396,11 +1396,11 @@
       <c r="F27" s="14">
         <v>2</v>
       </c>
-      <c r="G27" s="14">
-        <v>1</v>
-      </c>
-      <c r="H27" s="15">
-        <v>100</v>
+      <c r="G27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I27" s="14">
         <v>2</v>
@@ -1469,29 +1469,29 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="D29" s="14">
+        <v>1</v>
+      </c>
+      <c r="E29" s="15">
+        <v>-100</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H29" s="13" t="s">
-        <v>21</v>
+      <c r="G29" s="14">
+        <v>1</v>
+      </c>
+      <c r="H29" s="15">
+        <v>-100</v>
       </c>
       <c r="I29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="J29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K29" s="13" t="s">
-        <v>21</v>
+      <c r="J29" s="14">
+        <v>1</v>
+      </c>
+      <c r="K29" s="15">
+        <v>-100</v>
       </c>
       <c r="L29" s="13" t="s">
         <v>21</v>
@@ -1510,29 +1510,29 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="D30" s="14">
+        <v>1</v>
+      </c>
+      <c r="E30" s="15">
+        <v>-100</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H30" s="13" t="s">
-        <v>21</v>
+      <c r="G30" s="14">
+        <v>1</v>
+      </c>
+      <c r="H30" s="15">
+        <v>-100</v>
       </c>
       <c r="I30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="J30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K30" s="13" t="s">
-        <v>21</v>
+      <c r="J30" s="14">
+        <v>1</v>
+      </c>
+      <c r="K30" s="15">
+        <v>-100</v>
       </c>
       <c r="L30" s="13" t="s">
         <v>21</v>
@@ -1557,26 +1557,26 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="13" t="s">
-        <v>20</v>
+      <c r="F31" s="14">
+        <v>2</v>
       </c>
       <c r="G31" s="14">
         <v>2</v>
       </c>
       <c r="H31" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I31" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J31" s="14">
         <v>2</v>
       </c>
       <c r="K31" s="15">
-        <v>-50</v>
+        <v>50</v>
       </c>
       <c r="L31" s="15">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-111pct.xlsx
+++ b/data/source/weekly/cs-en-us-111pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -923,7 +923,7 @@
         <v>-66.666666666666</v>
       </c>
       <c r="M15" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="N15" s="15">
         <v>-50</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
+        <v>1</v>
+      </c>
+      <c r="D16" s="14">
         <v>2</v>
       </c>
-      <c r="D16" s="14">
-        <v>1</v>
-      </c>
       <c r="E16" s="15">
-        <v>100</v>
+        <v>-50</v>
       </c>
       <c r="F16" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G16" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H16" s="15">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="I16" s="14">
+        <v>8</v>
+      </c>
+      <c r="J16" s="14">
         <v>7</v>
       </c>
-      <c r="J16" s="14">
-        <v>5</v>
-      </c>
       <c r="K16" s="15">
-        <v>40</v>
+        <v>14.285714285714</v>
       </c>
       <c r="L16" s="15">
-        <v>-58.823529411764</v>
+        <v>-52.941176470588</v>
       </c>
       <c r="M16" s="15">
-        <v>-68.181818181818</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="N16" s="15">
-        <v>-91.954022988505</v>
+        <v>-91.304347826087</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,37 +978,37 @@
         <v>2</v>
       </c>
       <c r="D17" s="14">
+        <v>1</v>
+      </c>
+      <c r="E17" s="15">
+        <v>100</v>
+      </c>
+      <c r="F17" s="14">
         <v>6</v>
-      </c>
-      <c r="E17" s="15">
-        <v>-66.666666666666</v>
-      </c>
-      <c r="F17" s="14">
-        <v>7</v>
       </c>
       <c r="G17" s="14">
         <v>12</v>
       </c>
       <c r="H17" s="15">
-        <v>-41.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="I17" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J17" s="14">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K17" s="15">
-        <v>-48.148148148148</v>
+        <v>-46.428571428571</v>
       </c>
       <c r="L17" s="15">
-        <v>-26.315789473684</v>
+        <v>-25</v>
       </c>
       <c r="M17" s="15">
-        <v>16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="N17" s="15">
-        <v>-46.153846153846</v>
+        <v>-44.444444444444</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D18" s="14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E18" s="15">
-        <v>-50</v>
+        <v>-90</v>
       </c>
       <c r="F18" s="14">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G18" s="14">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H18" s="15">
-        <v>-38.095238095238</v>
+        <v>-56.521739130434</v>
       </c>
       <c r="I18" s="14">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J18" s="14">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="K18" s="15">
-        <v>-27.868852459016</v>
+        <v>-36.619718309859</v>
       </c>
       <c r="L18" s="15">
-        <v>-16.981132075471</v>
+        <v>-22.413793103448</v>
       </c>
       <c r="M18" s="15">
-        <v>-29.032258064516</v>
+        <v>-31.818181818181</v>
       </c>
       <c r="N18" s="15">
-        <v>-80.090497737556</v>
+        <v>-81.25</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D19" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E19" s="15">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="F19" s="14">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G19" s="14">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H19" s="15">
-        <v>18.421052631578</v>
+        <v>17.142857142857</v>
       </c>
       <c r="I19" s="14">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="J19" s="14">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="K19" s="15">
-        <v>36.734693877551</v>
+        <v>35.238095238095</v>
       </c>
       <c r="L19" s="15">
-        <v>27.619047619047</v>
+        <v>26.785714285714</v>
       </c>
       <c r="M19" s="15">
-        <v>52.272727272727</v>
+        <v>54.347826086956</v>
       </c>
       <c r="N19" s="15">
-        <v>15.517241379310</v>
+        <v>12.698412698412</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D20" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E20" s="15">
-        <v>40</v>
+        <v>-75</v>
       </c>
       <c r="F20" s="14">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G20" s="14">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H20" s="15">
-        <v>61.904761904761</v>
+        <v>52.631578947368</v>
       </c>
       <c r="I20" s="14">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J20" s="14">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="K20" s="15">
-        <v>37.254901960784</v>
+        <v>29.090909090909</v>
       </c>
       <c r="L20" s="15">
-        <v>16.666666666666</v>
+        <v>14.516129032258</v>
       </c>
       <c r="M20" s="15">
-        <v>150</v>
+        <v>129.032258064516</v>
       </c>
       <c r="N20" s="15">
-        <v>-89.928057553956</v>
+        <v>-90.620871862615</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="D21" s="17">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E21" s="18">
-        <v>-4.347826086956</v>
+        <v>-50</v>
       </c>
       <c r="F21" s="17">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="G21" s="17">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H21" s="18">
-        <v>8.510638297872</v>
+        <v>-3.225806451612</v>
       </c>
       <c r="I21" s="17">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="J21" s="17">
-        <v>245</v>
+        <v>269</v>
       </c>
       <c r="K21" s="18">
-        <v>10.204081632653</v>
+        <v>4.832713754646</v>
       </c>
       <c r="L21" s="18">
-        <v>5.058365758754</v>
+        <v>3.676470588235</v>
       </c>
       <c r="M21" s="18">
-        <v>26.760563380281</v>
+        <v>23.684210526315</v>
       </c>
       <c r="N21" s="18">
-        <v>-76.480836236933</v>
+        <v>-77.349397590361</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D24" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E24" s="15">
-        <v>-18.181818181818</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F24" s="14">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G24" s="14">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H24" s="15">
-        <v>-33.333333333333</v>
+        <v>-32.608695652173</v>
       </c>
       <c r="I24" s="14">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="J24" s="14">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="K24" s="15">
-        <v>-23.529411764705</v>
+        <v>-24.427480916030</v>
       </c>
       <c r="L24" s="15">
-        <v>-31.060606060606</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="M24" s="15">
-        <v>-19.469026548672</v>
+        <v>-19.512195121951</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1302,35 +1302,35 @@
       <c r="A25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="13" t="s">
-        <v>20</v>
+      <c r="C25" s="14">
+        <v>1</v>
       </c>
       <c r="D25" s="14">
         <v>1</v>
       </c>
       <c r="E25" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F25" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G25" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H25" s="15">
-        <v>-75</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I25" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J25" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K25" s="15">
-        <v>-68.421052631578</v>
+        <v>-65</v>
       </c>
       <c r="L25" s="15">
-        <v>-76.923076923076</v>
+        <v>-75.862068965517</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,34 +1347,34 @@
         <v>4</v>
       </c>
       <c r="D26" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E26" s="15">
-        <v>-42.857142857142</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="F26" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G26" s="14">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="H26" s="15">
-        <v>-13.333333333333</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="I26" s="14">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="J26" s="14">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="K26" s="15">
+        <v>-10.810810810810</v>
+      </c>
+      <c r="L26" s="15">
+        <v>-23.255813953488</v>
+      </c>
+      <c r="M26" s="15">
         <v>0</v>
-      </c>
-      <c r="L26" s="15">
-        <v>-30</v>
-      </c>
-      <c r="M26" s="15">
-        <v>-9.677419354838</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1425,8 +1425,8 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="14">
+        <v>1</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>20</v>
@@ -1435,7 +1435,7 @@
         <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G28" s="13" t="s">
         <v>20</v>
@@ -1444,7 +1444,7 @@
         <v>21</v>
       </c>
       <c r="I28" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J28" s="13" t="s">
         <v>20</v>
@@ -1453,7 +1453,7 @@
         <v>21</v>
       </c>
       <c r="L28" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,11 +1469,11 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="14">
-        <v>1</v>
-      </c>
-      <c r="E29" s="15">
-        <v>-100</v>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>20</v>
@@ -1510,11 +1510,11 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="14">
-        <v>1</v>
-      </c>
-      <c r="E30" s="15">
-        <v>-100</v>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>20</v>
@@ -1558,25 +1558,25 @@
         <v>21</v>
       </c>
       <c r="F31" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G31" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H31" s="15">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I31" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J31" s="14">
         <v>2</v>
       </c>
       <c r="K31" s="15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L31" s="15">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-111pct.xlsx
+++ b/data/source/weekly/cs-en-us-111pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -936,120 +936,120 @@
       <c r="C16" s="14">
         <v>1</v>
       </c>
-      <c r="D16" s="14">
-        <v>2</v>
-      </c>
-      <c r="E16" s="15">
-        <v>-50</v>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F16" s="14">
+        <v>4</v>
+      </c>
+      <c r="G16" s="14">
         <v>3</v>
       </c>
-      <c r="G16" s="14">
-        <v>4</v>
-      </c>
       <c r="H16" s="15">
-        <v>-25</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I16" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J16" s="14">
         <v>7</v>
       </c>
       <c r="K16" s="15">
-        <v>14.285714285714</v>
+        <v>28.571428571428</v>
       </c>
       <c r="L16" s="15">
-        <v>-52.941176470588</v>
+        <v>-50</v>
       </c>
       <c r="M16" s="15">
-        <v>-63.636363636363</v>
+        <v>-60.869565217391</v>
       </c>
       <c r="N16" s="15">
-        <v>-91.304347826087</v>
+        <v>-91.176470588235</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="14">
-        <v>2</v>
+      <c r="C17" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D17" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E17" s="15">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="F17" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G17" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H17" s="15">
-        <v>-50</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="I17" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J17" s="14">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K17" s="15">
-        <v>-46.428571428571</v>
+        <v>-45.161290322580</v>
       </c>
       <c r="L17" s="15">
-        <v>-25</v>
+        <v>-15</v>
       </c>
       <c r="M17" s="15">
-        <v>0</v>
+        <v>13.333333333333</v>
       </c>
       <c r="N17" s="15">
-        <v>-44.444444444444</v>
+        <v>-43.333333333333</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
-        <v>1</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D18" s="14">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E18" s="15">
-        <v>-90</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G18" s="14">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H18" s="15">
-        <v>-56.521739130434</v>
+        <v>-69.230769230769</v>
       </c>
       <c r="I18" s="14">
         <v>45</v>
       </c>
       <c r="J18" s="14">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="K18" s="15">
+        <v>-40.789473684210</v>
+      </c>
+      <c r="L18" s="15">
+        <v>-29.6875</v>
+      </c>
+      <c r="M18" s="15">
         <v>-36.619718309859</v>
       </c>
-      <c r="L18" s="15">
-        <v>-22.413793103448</v>
-      </c>
-      <c r="M18" s="15">
-        <v>-31.818181818181</v>
-      </c>
       <c r="N18" s="15">
-        <v>-81.25</v>
+        <v>-82.352941176470</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D19" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E19" s="15">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="F19" s="14">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G19" s="14">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="H19" s="15">
-        <v>17.142857142857</v>
+        <v>58.333333333333</v>
       </c>
       <c r="I19" s="14">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="J19" s="14">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="K19" s="15">
-        <v>35.238095238095</v>
+        <v>39.449541284403</v>
       </c>
       <c r="L19" s="15">
-        <v>26.785714285714</v>
+        <v>28.813559322033</v>
       </c>
       <c r="M19" s="15">
-        <v>54.347826086956</v>
+        <v>56.701030927835</v>
       </c>
       <c r="N19" s="15">
-        <v>12.698412698412</v>
+        <v>13.432835820895</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D20" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E20" s="15">
-        <v>-75</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F20" s="14">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="G20" s="14">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H20" s="15">
-        <v>52.631578947368</v>
+        <v>69.230769230769</v>
       </c>
       <c r="I20" s="14">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="J20" s="14">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K20" s="15">
-        <v>29.090909090909</v>
+        <v>31.034482758620</v>
       </c>
       <c r="L20" s="15">
-        <v>14.516129032258</v>
+        <v>7.042253521126</v>
       </c>
       <c r="M20" s="15">
-        <v>129.032258064516</v>
+        <v>123.529411764706</v>
       </c>
       <c r="N20" s="15">
-        <v>-90.620871862615</v>
+        <v>-90.617283950617</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D21" s="17">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="E21" s="18">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="F21" s="17">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G21" s="17">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="H21" s="18">
-        <v>-3.225806451612</v>
+        <v>1.265822784810</v>
       </c>
       <c r="I21" s="17">
-        <v>282</v>
+        <v>300</v>
       </c>
       <c r="J21" s="17">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="K21" s="18">
-        <v>4.832713754646</v>
+        <v>5.633802816901</v>
       </c>
       <c r="L21" s="18">
-        <v>3.676470588235</v>
+        <v>2.040816326530</v>
       </c>
       <c r="M21" s="18">
-        <v>23.684210526315</v>
+        <v>23.966942148760</v>
       </c>
       <c r="N21" s="18">
-        <v>-77.349397590361</v>
+        <v>-77.511244377811</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D24" s="14">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E24" s="15">
-        <v>-33.333333333333</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="F24" s="14">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G24" s="14">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H24" s="15">
-        <v>-32.608695652173</v>
+        <v>-26.530612244898</v>
       </c>
       <c r="I24" s="14">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="J24" s="14">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="K24" s="15">
-        <v>-24.427480916030</v>
+        <v>-23.287671232876</v>
       </c>
       <c r="L24" s="15">
-        <v>-30.769230769230</v>
+        <v>-26.797385620915</v>
       </c>
       <c r="M24" s="15">
-        <v>-19.512195121951</v>
+        <v>-14.503816793893</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D25" s="14">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E25" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="F25" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G25" s="14">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H25" s="15">
-        <v>-66.666666666666</v>
+        <v>-61.538461538461</v>
       </c>
       <c r="I25" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J25" s="14">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="K25" s="15">
-        <v>-65</v>
+        <v>-61.538461538461</v>
       </c>
       <c r="L25" s="15">
-        <v>-75.862068965517</v>
+        <v>-69.696969696969</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,34 +1347,34 @@
         <v>4</v>
       </c>
       <c r="D26" s="14">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E26" s="15">
-        <v>-55.555555555555</v>
+        <v>-20</v>
       </c>
       <c r="F26" s="14">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G26" s="14">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H26" s="15">
-        <v>-28.571428571428</v>
+        <v>-44</v>
       </c>
       <c r="I26" s="14">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J26" s="14">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="K26" s="15">
-        <v>-10.810810810810</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="L26" s="15">
-        <v>-23.255813953488</v>
+        <v>-23.913043478260</v>
       </c>
       <c r="M26" s="15">
-        <v>0</v>
+        <v>2.941176470588</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,32 +1387,32 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>-100</v>
       </c>
       <c r="F27" s="14">
         <v>2</v>
       </c>
-      <c r="G27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H27" s="13" t="s">
-        <v>21</v>
+      <c r="G27" s="14">
+        <v>1</v>
+      </c>
+      <c r="H27" s="15">
+        <v>100</v>
       </c>
       <c r="I27" s="14">
         <v>2</v>
       </c>
       <c r="J27" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K27" s="15">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="L27" s="15">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1444,7 +1444,7 @@
         <v>21</v>
       </c>
       <c r="I28" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J28" s="13" t="s">
         <v>20</v>
@@ -1453,7 +1453,7 @@
         <v>21</v>
       </c>
       <c r="L28" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1551,11 +1551,11 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="14">
+        <v>1</v>
+      </c>
+      <c r="E31" s="15">
+        <v>-100</v>
       </c>
       <c r="F31" s="14">
         <v>3</v>
@@ -1570,10 +1570,10 @@
         <v>4</v>
       </c>
       <c r="J31" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K31" s="15">
-        <v>100</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L31" s="15">
         <v>300</v>

--- a/data/source/weekly/cs-en-us-111pct.xlsx
+++ b/data/source/weekly/cs-en-us-111pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -854,26 +854,26 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
+      <c r="D14" s="14">
+        <v>1</v>
+      </c>
+      <c r="E14" s="15">
+        <v>-100</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H14" s="13" t="s">
-        <v>21</v>
+      <c r="G14" s="14">
+        <v>1</v>
+      </c>
+      <c r="H14" s="15">
+        <v>-100</v>
       </c>
       <c r="I14" s="13" t="s">
         <v>20</v>
       </c>
       <c r="J14" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K14" s="15">
         <v>-100</v>
@@ -901,8 +901,8 @@
       <c r="E15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F15" s="14">
-        <v>1</v>
+      <c r="F15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>20</v>
@@ -933,8 +933,8 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="14">
-        <v>1</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D16" s="13" t="s">
         <v>20</v>
@@ -967,89 +967,89 @@
         <v>-60.869565217391</v>
       </c>
       <c r="N16" s="15">
-        <v>-91.176470588235</v>
+        <v>-91.743119266055</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="13" t="s">
-        <v>20</v>
+      <c r="C17" s="14">
+        <v>2</v>
       </c>
       <c r="D17" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E17" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="F17" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G17" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H17" s="15">
-        <v>-46.153846153846</v>
+        <v>-64.285714285714</v>
       </c>
       <c r="I17" s="14">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J17" s="14">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="K17" s="15">
-        <v>-45.161290322580</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="L17" s="15">
-        <v>-15</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="M17" s="15">
-        <v>13.333333333333</v>
+        <v>17.647058823529</v>
       </c>
       <c r="N17" s="15">
-        <v>-43.333333333333</v>
+        <v>-39.393939393939</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="14">
+        <v>3</v>
       </c>
       <c r="D18" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E18" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="F18" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G18" s="14">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H18" s="15">
-        <v>-69.230769230769</v>
+        <v>-74.074074074074</v>
       </c>
       <c r="I18" s="14">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="J18" s="14">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K18" s="15">
-        <v>-40.789473684210</v>
+        <v>-41.463414634146</v>
       </c>
       <c r="L18" s="15">
-        <v>-29.6875</v>
+        <v>-31.428571428571</v>
       </c>
       <c r="M18" s="15">
-        <v>-36.619718309859</v>
+        <v>-35.135135135135</v>
       </c>
       <c r="N18" s="15">
-        <v>-82.352941176470</v>
+        <v>-82.417582417582</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D19" s="14">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E19" s="15">
-        <v>125</v>
+        <v>-72.727272727272</v>
       </c>
       <c r="F19" s="14">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="G19" s="14">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="H19" s="15">
-        <v>58.333333333333</v>
+        <v>0</v>
       </c>
       <c r="I19" s="14">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="J19" s="14">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="K19" s="15">
-        <v>39.449541284403</v>
+        <v>30</v>
       </c>
       <c r="L19" s="15">
-        <v>28.813559322033</v>
+        <v>16.417910447761</v>
       </c>
       <c r="M19" s="15">
-        <v>56.701030927835</v>
+        <v>40.540540540540</v>
       </c>
       <c r="N19" s="15">
-        <v>13.432835820895</v>
+        <v>13.043478260869</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
+        <v>8</v>
+      </c>
+      <c r="D20" s="14">
         <v>5</v>
       </c>
-      <c r="D20" s="14">
-        <v>3</v>
-      </c>
       <c r="E20" s="15">
-        <v>66.666666666666</v>
+        <v>60</v>
       </c>
       <c r="F20" s="14">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G20" s="14">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H20" s="15">
-        <v>69.230769230769</v>
+        <v>23.529411764705</v>
       </c>
       <c r="I20" s="14">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="J20" s="14">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="K20" s="15">
-        <v>31.034482758620</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L20" s="15">
-        <v>7.042253521126</v>
+        <v>10.526315789473</v>
       </c>
       <c r="M20" s="15">
-        <v>123.529411764706</v>
+        <v>115.384615384615</v>
       </c>
       <c r="N20" s="15">
-        <v>-90.617283950617</v>
+        <v>-90.432801822323</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D21" s="17">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="E21" s="18">
-        <v>0</v>
+        <v>-40.740740740740</v>
       </c>
       <c r="F21" s="17">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="G21" s="17">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H21" s="18">
-        <v>1.265822784810</v>
+        <v>-28.089887640449</v>
       </c>
       <c r="I21" s="17">
-        <v>300</v>
+        <v>318</v>
       </c>
       <c r="J21" s="17">
-        <v>284</v>
+        <v>311</v>
       </c>
       <c r="K21" s="18">
-        <v>5.633802816901</v>
+        <v>2.250803858520</v>
       </c>
       <c r="L21" s="18">
-        <v>2.040816326530</v>
+        <v>-1.547987616099</v>
       </c>
       <c r="M21" s="18">
-        <v>23.966942148760</v>
+        <v>19.548872180451</v>
       </c>
       <c r="N21" s="18">
-        <v>-77.511244377811</v>
+        <v>-77.824267782426</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D24" s="14">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E24" s="15">
-        <v>-13.333333333333</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F24" s="14">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G24" s="14">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H24" s="15">
-        <v>-26.530612244898</v>
+        <v>-24</v>
       </c>
       <c r="I24" s="14">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="J24" s="14">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="K24" s="15">
-        <v>-23.287671232876</v>
+        <v>-24.050632911392</v>
       </c>
       <c r="L24" s="15">
-        <v>-26.797385620915</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="M24" s="15">
-        <v>-14.503816793893</v>
+        <v>-13.669064748201</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1302,35 +1302,35 @@
       <c r="A25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="14">
+      <c r="C25" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D25" s="14">
         <v>3</v>
       </c>
-      <c r="D25" s="14">
-        <v>6</v>
-      </c>
       <c r="E25" s="15">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="F25" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G25" s="14">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H25" s="15">
-        <v>-61.538461538461</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="I25" s="14">
         <v>10</v>
       </c>
       <c r="J25" s="14">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K25" s="15">
-        <v>-61.538461538461</v>
+        <v>-65.517241379310</v>
       </c>
       <c r="L25" s="15">
-        <v>-69.696969696969</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1346,35 +1346,35 @@
       <c r="C26" s="14">
         <v>4</v>
       </c>
-      <c r="D26" s="14">
-        <v>5</v>
-      </c>
-      <c r="E26" s="15">
-        <v>-20</v>
+      <c r="D26" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E26" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F26" s="14">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G26" s="14">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H26" s="15">
-        <v>-44</v>
+        <v>-19.047619047619</v>
       </c>
       <c r="I26" s="14">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="J26" s="14">
         <v>42</v>
       </c>
       <c r="K26" s="15">
-        <v>-16.666666666666</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="L26" s="15">
-        <v>-23.913043478260</v>
+        <v>-22</v>
       </c>
       <c r="M26" s="15">
-        <v>2.941176470588</v>
+        <v>5.405405405405</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,20 +1387,20 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F27" s="14">
-        <v>2</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G27" s="14">
         <v>1</v>
       </c>
       <c r="H27" s="15">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="I27" s="14">
         <v>2</v>
@@ -1425,27 +1425,27 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" s="14">
         <v>1</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F28" s="14">
+      <c r="G28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H28" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="I28" s="14">
         <v>2</v>
       </c>
-      <c r="G28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H28" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="I28" s="14">
-        <v>3</v>
-      </c>
       <c r="J28" s="13" t="s">
         <v>20</v>
       </c>
@@ -1453,7 +1453,7 @@
         <v>21</v>
       </c>
       <c r="L28" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,17 +1469,17 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="D29" s="14">
+        <v>1</v>
+      </c>
+      <c r="E29" s="15">
+        <v>-100</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H29" s="15">
         <v>-100</v>
@@ -1488,7 +1488,7 @@
         <v>20</v>
       </c>
       <c r="J29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K29" s="15">
         <v>-100</v>
@@ -1510,17 +1510,17 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="D30" s="14">
+        <v>1</v>
+      </c>
+      <c r="E30" s="15">
+        <v>-100</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H30" s="15">
         <v>-100</v>
@@ -1529,7 +1529,7 @@
         <v>20</v>
       </c>
       <c r="J30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K30" s="15">
         <v>-100</v>
@@ -1551,20 +1551,20 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="14">
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F31" s="14">
         <v>1</v>
-      </c>
-      <c r="E31" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F31" s="14">
-        <v>3</v>
       </c>
       <c r="G31" s="14">
         <v>1</v>
       </c>
       <c r="H31" s="15">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I31" s="14">
         <v>4</v>

--- a/data/source/weekly/cs-en-us-111pct.xlsx
+++ b/data/source/weekly/cs-en-us-111pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -854,11 +854,11 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="14">
-        <v>1</v>
-      </c>
-      <c r="E14" s="15">
-        <v>-100</v>
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
@@ -943,13 +943,13 @@
         <v>21</v>
       </c>
       <c r="F16" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G16" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H16" s="15">
-        <v>33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="I16" s="14">
         <v>9</v>
@@ -967,7 +967,7 @@
         <v>-60.869565217391</v>
       </c>
       <c r="N16" s="15">
-        <v>-91.743119266055</v>
+        <v>-92.105263157894</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D17" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E17" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="F17" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G17" s="14">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H17" s="15">
-        <v>-64.285714285714</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="I17" s="14">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J17" s="14">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K17" s="15">
-        <v>-42.857142857142</v>
+        <v>-39.473684210526</v>
       </c>
       <c r="L17" s="15">
-        <v>-9.090909090909</v>
+        <v>-11.538461538461</v>
       </c>
       <c r="M17" s="15">
-        <v>17.647058823529</v>
+        <v>27.777777777777</v>
       </c>
       <c r="N17" s="15">
-        <v>-39.393939393939</v>
+        <v>-36.111111111111</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D18" s="14">
         <v>6</v>
       </c>
       <c r="E18" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F18" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G18" s="14">
         <v>27</v>
       </c>
       <c r="H18" s="15">
-        <v>-74.074074074074</v>
+        <v>-77.777777777777</v>
       </c>
       <c r="I18" s="14">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="J18" s="14">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="K18" s="15">
-        <v>-41.463414634146</v>
+        <v>-43.181818181818</v>
       </c>
       <c r="L18" s="15">
-        <v>-31.428571428571</v>
+        <v>-35.897435897435</v>
       </c>
       <c r="M18" s="15">
-        <v>-35.135135135135</v>
+        <v>-37.5</v>
       </c>
       <c r="N18" s="15">
-        <v>-82.417582417582</v>
+        <v>-83.277591973244</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D19" s="14">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E19" s="15">
-        <v>-72.727272727272</v>
+        <v>250</v>
       </c>
       <c r="F19" s="14">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G19" s="14">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H19" s="15">
-        <v>0</v>
+        <v>26.923076923076</v>
       </c>
       <c r="I19" s="14">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="J19" s="14">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="K19" s="15">
-        <v>30</v>
+        <v>37.096774193548</v>
       </c>
       <c r="L19" s="15">
-        <v>16.417910447761</v>
+        <v>20.567375886524</v>
       </c>
       <c r="M19" s="15">
-        <v>40.540540540540</v>
+        <v>42.857142857142</v>
       </c>
       <c r="N19" s="15">
-        <v>13.043478260869</v>
+        <v>14.093959731543</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D20" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E20" s="15">
-        <v>60</v>
+        <v>42.857142857142</v>
       </c>
       <c r="F20" s="14">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G20" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H20" s="15">
-        <v>23.529411764705</v>
+        <v>26.315789473684</v>
       </c>
       <c r="I20" s="14">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="J20" s="14">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="K20" s="15">
-        <v>33.333333333333</v>
+        <v>34.285714285714</v>
       </c>
       <c r="L20" s="15">
-        <v>10.526315789473</v>
+        <v>14.634146341463</v>
       </c>
       <c r="M20" s="15">
-        <v>115.384615384615</v>
+        <v>118.604651162791</v>
       </c>
       <c r="N20" s="15">
-        <v>-90.432801822323</v>
+        <v>-90.187891440501</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="D21" s="17">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="E21" s="18">
-        <v>-40.740740740740</v>
+        <v>45</v>
       </c>
       <c r="F21" s="17">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="G21" s="17">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H21" s="18">
-        <v>-28.089887640449</v>
+        <v>-16.279069767441</v>
       </c>
       <c r="I21" s="17">
-        <v>318</v>
+        <v>347</v>
       </c>
       <c r="J21" s="17">
-        <v>311</v>
+        <v>331</v>
       </c>
       <c r="K21" s="18">
-        <v>2.250803858520</v>
+        <v>4.833836858006</v>
       </c>
       <c r="L21" s="18">
-        <v>-1.547987616099</v>
+        <v>-0.287356321839</v>
       </c>
       <c r="M21" s="18">
-        <v>19.548872180451</v>
+        <v>21.754385964912</v>
       </c>
       <c r="N21" s="18">
-        <v>-77.824267782426</v>
+        <v>-77.742142398973</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D24" s="14">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E24" s="15">
-        <v>-33.333333333333</v>
+        <v>150</v>
       </c>
       <c r="F24" s="14">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G24" s="14">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="H24" s="15">
-        <v>-24</v>
+        <v>-9.302325581395</v>
       </c>
       <c r="I24" s="14">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="J24" s="14">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="K24" s="15">
-        <v>-24.050632911392</v>
+        <v>-19.753086419753</v>
       </c>
       <c r="L24" s="15">
-        <v>-23.076923076923</v>
+        <v>-21.686746987951</v>
       </c>
       <c r="M24" s="15">
-        <v>-13.669064748201</v>
+        <v>-11.564625850340</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1302,35 +1302,35 @@
       <c r="A25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="13" t="s">
-        <v>20</v>
+      <c r="C25" s="14">
+        <v>1</v>
       </c>
       <c r="D25" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E25" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="F25" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G25" s="14">
+        <v>12</v>
+      </c>
+      <c r="H25" s="15">
+        <v>-58.333333333333</v>
+      </c>
+      <c r="I25" s="14">
         <v>11</v>
       </c>
-      <c r="H25" s="15">
-        <v>-63.636363636363</v>
-      </c>
-      <c r="I25" s="14">
-        <v>10</v>
-      </c>
       <c r="J25" s="14">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K25" s="15">
-        <v>-65.517241379310</v>
+        <v>-64.516129032258</v>
       </c>
       <c r="L25" s="15">
-        <v>-71.428571428571</v>
+        <v>-71.052631578947</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>4</v>
-      </c>
-      <c r="D26" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E26" s="13" t="s">
-        <v>21</v>
+        <v>2</v>
+      </c>
+      <c r="D26" s="14">
+        <v>5</v>
+      </c>
+      <c r="E26" s="15">
+        <v>-60</v>
       </c>
       <c r="F26" s="14">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G26" s="14">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H26" s="15">
-        <v>-19.047619047619</v>
+        <v>-26.315789473684</v>
       </c>
       <c r="I26" s="14">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J26" s="14">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="K26" s="15">
-        <v>-7.142857142857</v>
+        <v>-12.765957446808</v>
       </c>
       <c r="L26" s="15">
-        <v>-22</v>
+        <v>-25.454545454545</v>
       </c>
       <c r="M26" s="15">
-        <v>5.405405405405</v>
+        <v>-4.651162790697</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1469,17 +1469,17 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="14">
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G29" s="14">
         <v>1</v>
-      </c>
-      <c r="E29" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G29" s="14">
-        <v>2</v>
       </c>
       <c r="H29" s="15">
         <v>-100</v>
@@ -1510,17 +1510,17 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="14">
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G30" s="14">
         <v>1</v>
-      </c>
-      <c r="E30" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G30" s="14">
-        <v>2</v>
       </c>
       <c r="H30" s="15">
         <v>-100</v>
@@ -1557,14 +1557,14 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="14">
-        <v>1</v>
+      <c r="F31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G31" s="14">
         <v>1</v>
       </c>
       <c r="H31" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I31" s="14">
         <v>4</v>

--- a/data/source/weekly/cs-en-us-111pct.xlsx
+++ b/data/source/weekly/cs-en-us-111pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -926,15 +926,15 @@
         <v>-50</v>
       </c>
       <c r="N15" s="15">
-        <v>-50</v>
+        <v>-75</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
+      <c r="C16" s="14">
+        <v>2</v>
       </c>
       <c r="D16" s="13" t="s">
         <v>20</v>
@@ -943,31 +943,31 @@
         <v>21</v>
       </c>
       <c r="F16" s="14">
-        <v>2</v>
-      </c>
-      <c r="G16" s="14">
-        <v>2</v>
-      </c>
-      <c r="H16" s="15">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="G16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H16" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I16" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J16" s="14">
         <v>7</v>
       </c>
       <c r="K16" s="15">
-        <v>28.571428571428</v>
+        <v>57.142857142857</v>
       </c>
       <c r="L16" s="15">
-        <v>-50</v>
+        <v>-42.105263157894</v>
       </c>
       <c r="M16" s="15">
-        <v>-60.869565217391</v>
+        <v>-54.166666666666</v>
       </c>
       <c r="N16" s="15">
-        <v>-92.105263157894</v>
+        <v>-90.598290598290</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D17" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E17" s="15">
-        <v>0</v>
+        <v>-75</v>
       </c>
       <c r="F17" s="14">
         <v>7</v>
       </c>
       <c r="G17" s="14">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H17" s="15">
-        <v>-36.363636363636</v>
+        <v>-50</v>
       </c>
       <c r="I17" s="14">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J17" s="14">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K17" s="15">
-        <v>-39.473684210526</v>
+        <v>-40.476190476190</v>
       </c>
       <c r="L17" s="15">
-        <v>-11.538461538461</v>
+        <v>-7.407407407407</v>
       </c>
       <c r="M17" s="15">
-        <v>27.777777777777</v>
+        <v>31.578947368421</v>
       </c>
       <c r="N17" s="15">
-        <v>-36.111111111111</v>
+        <v>-35.897435897435</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,37 +1019,37 @@
         <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E18" s="15">
-        <v>-66.666666666666</v>
+        <v>-60</v>
       </c>
       <c r="F18" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G18" s="14">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="H18" s="15">
-        <v>-77.777777777777</v>
+        <v>-68.181818181818</v>
       </c>
       <c r="I18" s="14">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="J18" s="14">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="K18" s="15">
-        <v>-43.181818181818</v>
+        <v>-44.086021505376</v>
       </c>
       <c r="L18" s="15">
-        <v>-35.897435897435</v>
+        <v>-36.585365853658</v>
       </c>
       <c r="M18" s="15">
-        <v>-37.5</v>
+        <v>-38.823529411764</v>
       </c>
       <c r="N18" s="15">
-        <v>-83.277591973244</v>
+        <v>-83.492063492063</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D19" s="14">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E19" s="15">
-        <v>250</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="F19" s="14">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G19" s="14">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H19" s="15">
-        <v>26.923076923076</v>
+        <v>3.333333333333</v>
       </c>
       <c r="I19" s="14">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="J19" s="14">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="K19" s="15">
-        <v>37.096774193548</v>
+        <v>30.370370370370</v>
       </c>
       <c r="L19" s="15">
-        <v>20.567375886524</v>
+        <v>15.789473684210</v>
       </c>
       <c r="M19" s="15">
-        <v>42.857142857142</v>
+        <v>40.8</v>
       </c>
       <c r="N19" s="15">
-        <v>14.093959731543</v>
+        <v>13.548387096774</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D20" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E20" s="15">
-        <v>42.857142857142</v>
+        <v>-50</v>
       </c>
       <c r="F20" s="14">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G20" s="14">
         <v>19</v>
       </c>
       <c r="H20" s="15">
-        <v>26.315789473684</v>
+        <v>31.578947368421</v>
       </c>
       <c r="I20" s="14">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="J20" s="14">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="K20" s="15">
-        <v>34.285714285714</v>
+        <v>29.729729729729</v>
       </c>
       <c r="L20" s="15">
-        <v>14.634146341463</v>
+        <v>12.941176470588</v>
       </c>
       <c r="M20" s="15">
-        <v>118.604651162791</v>
+        <v>113.333333333333</v>
       </c>
       <c r="N20" s="15">
-        <v>-90.187891440501</v>
+        <v>-90.606653620352</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="D21" s="17">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E21" s="18">
-        <v>45</v>
+        <v>-50</v>
       </c>
       <c r="F21" s="17">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G21" s="17">
         <v>86</v>
       </c>
       <c r="H21" s="18">
-        <v>-16.279069767441</v>
+        <v>-15.116279069767</v>
       </c>
       <c r="I21" s="17">
-        <v>347</v>
+        <v>361</v>
       </c>
       <c r="J21" s="17">
-        <v>331</v>
+        <v>355</v>
       </c>
       <c r="K21" s="18">
-        <v>4.833836858006</v>
+        <v>1.690140845070</v>
       </c>
       <c r="L21" s="18">
-        <v>-0.287356321839</v>
+        <v>-1.902173913043</v>
       </c>
       <c r="M21" s="18">
-        <v>21.754385964912</v>
+        <v>20.333333333333</v>
       </c>
       <c r="N21" s="18">
-        <v>-77.742142398973</v>
+        <v>-78.160919540229</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D24" s="14">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="E24" s="15">
-        <v>150</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="F24" s="14">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G24" s="14">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H24" s="15">
-        <v>-9.302325581395</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="I24" s="14">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="J24" s="14">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="K24" s="15">
-        <v>-19.753086419753</v>
+        <v>-21.714285714285</v>
       </c>
       <c r="L24" s="15">
-        <v>-21.686746987951</v>
+        <v>-18.934911242603</v>
       </c>
       <c r="M24" s="15">
-        <v>-11.564625850340</v>
+        <v>-13.291139240506</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1302,35 +1302,35 @@
       <c r="A25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="14">
-        <v>1</v>
+      <c r="C25" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D25" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E25" s="15">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="F25" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G25" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H25" s="15">
-        <v>-58.333333333333</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="I25" s="14">
         <v>11</v>
       </c>
       <c r="J25" s="14">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K25" s="15">
-        <v>-64.516129032258</v>
+        <v>-67.647058823529</v>
       </c>
       <c r="L25" s="15">
-        <v>-71.052631578947</v>
+        <v>-71.794871794871</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,34 +1347,34 @@
         <v>2</v>
       </c>
       <c r="D26" s="14">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E26" s="15">
-        <v>-60</v>
+        <v>-77.777777777777</v>
       </c>
       <c r="F26" s="14">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G26" s="14">
         <v>19</v>
       </c>
       <c r="H26" s="15">
-        <v>-26.315789473684</v>
+        <v>-36.842105263157</v>
       </c>
       <c r="I26" s="14">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J26" s="14">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="K26" s="15">
-        <v>-12.765957446808</v>
+        <v>-23.214285714285</v>
       </c>
       <c r="L26" s="15">
-        <v>-25.454545454545</v>
+        <v>-27.118644067796</v>
       </c>
       <c r="M26" s="15">
-        <v>-4.651162790697</v>
+        <v>-2.272727272727</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="C28" s="14">
+        <v>1</v>
+      </c>
+      <c r="D28" s="14">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15">
+        <v>0</v>
       </c>
       <c r="F28" s="14">
         <v>1</v>
       </c>
-      <c r="G28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H28" s="13" t="s">
-        <v>21</v>
+      <c r="G28" s="14">
+        <v>1</v>
+      </c>
+      <c r="H28" s="15">
+        <v>0</v>
       </c>
       <c r="I28" s="14">
-        <v>2</v>
-      </c>
-      <c r="J28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K28" s="13" t="s">
-        <v>21</v>
+        <v>3</v>
+      </c>
+      <c r="J28" s="14">
+        <v>1</v>
+      </c>
+      <c r="K28" s="15">
+        <v>200</v>
       </c>
       <c r="L28" s="15">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1551,17 +1551,17 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="14">
+        <v>1</v>
+      </c>
+      <c r="E31" s="15">
+        <v>-100</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G31" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H31" s="15">
         <v>-100</v>
@@ -1570,10 +1570,10 @@
         <v>4</v>
       </c>
       <c r="J31" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K31" s="15">
-        <v>33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="L31" s="15">
         <v>300</v>
@@ -1607,8 +1607,8 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="13" t="s">
-        <v>20</v>
+      <c r="C33" s="14">
+        <v>1</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>
@@ -1616,8 +1616,8 @@
       <c r="E33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F33" s="13" t="s">
-        <v>20</v>
+      <c r="F33" s="14">
+        <v>1</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>20</v>
@@ -1625,8 +1625,8 @@
       <c r="H33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I33" s="13" t="s">
-        <v>20</v>
+      <c r="I33" s="14">
+        <v>1</v>
       </c>
       <c r="J33" s="13" t="s">
         <v>20</v>
@@ -1635,7 +1635,7 @@
         <v>21</v>
       </c>
       <c r="L33" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-111pct.xlsx
+++ b/data/source/weekly/cs-en-us-111pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -926,7 +926,7 @@
         <v>-50</v>
       </c>
       <c r="N15" s="15">
-        <v>-75</v>
+        <v>-80</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
+        <v>1</v>
+      </c>
+      <c r="D16" s="14">
         <v>2</v>
       </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
+      <c r="E16" s="15">
+        <v>-50</v>
       </c>
       <c r="F16" s="14">
         <v>3</v>
       </c>
-      <c r="G16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H16" s="13" t="s">
-        <v>21</v>
+      <c r="G16" s="14">
+        <v>2</v>
+      </c>
+      <c r="H16" s="15">
+        <v>50</v>
       </c>
       <c r="I16" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J16" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K16" s="15">
-        <v>57.142857142857</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L16" s="15">
-        <v>-42.105263157894</v>
+        <v>-36.842105263157</v>
       </c>
       <c r="M16" s="15">
-        <v>-54.166666666666</v>
+        <v>-53.846153846153</v>
       </c>
       <c r="N16" s="15">
-        <v>-90.598290598290</v>
+        <v>-90.322580645161</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D17" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E17" s="15">
-        <v>-75</v>
+        <v>100</v>
       </c>
       <c r="F17" s="14">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G17" s="14">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H17" s="15">
-        <v>-50</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="I17" s="14">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J17" s="14">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K17" s="15">
-        <v>-40.476190476190</v>
+        <v>-34.090909090909</v>
       </c>
       <c r="L17" s="15">
-        <v>-7.407407407407</v>
+        <v>3.571428571428</v>
       </c>
       <c r="M17" s="15">
-        <v>31.578947368421</v>
+        <v>38.095238095238</v>
       </c>
       <c r="N17" s="15">
-        <v>-35.897435897435</v>
+        <v>-35.555555555555</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D18" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E18" s="15">
-        <v>-60</v>
+        <v>0</v>
       </c>
       <c r="F18" s="14">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G18" s="14">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H18" s="15">
-        <v>-68.181818181818</v>
+        <v>-47.619047619047</v>
       </c>
       <c r="I18" s="14">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="J18" s="14">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="K18" s="15">
-        <v>-44.086021505376</v>
+        <v>-42.268041237113</v>
       </c>
       <c r="L18" s="15">
-        <v>-36.585365853658</v>
+        <v>-35.632183908046</v>
       </c>
       <c r="M18" s="15">
-        <v>-38.823529411764</v>
+        <v>-35.632183908046</v>
       </c>
       <c r="N18" s="15">
-        <v>-83.492063492063</v>
+        <v>-83.183183183183</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D19" s="14">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E19" s="15">
-        <v>-54.545454545454</v>
+        <v>-25</v>
       </c>
       <c r="F19" s="14">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G19" s="14">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H19" s="15">
-        <v>3.333333333333</v>
+        <v>-14.705882352941</v>
       </c>
       <c r="I19" s="14">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="J19" s="14">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="K19" s="15">
-        <v>30.370370370370</v>
+        <v>27.972027972028</v>
       </c>
       <c r="L19" s="15">
-        <v>15.789473684210</v>
+        <v>7.647058823529</v>
       </c>
       <c r="M19" s="15">
-        <v>40.8</v>
+        <v>36.567164179104</v>
       </c>
       <c r="N19" s="15">
-        <v>13.548387096774</v>
+        <v>10.240963855421</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D20" s="14">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E20" s="15">
-        <v>-50</v>
+        <v>-72.727272727272</v>
       </c>
       <c r="F20" s="14">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G20" s="14">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="H20" s="15">
-        <v>31.578947368421</v>
+        <v>-14.814814814814</v>
       </c>
       <c r="I20" s="14">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="J20" s="14">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="K20" s="15">
-        <v>29.729729729729</v>
+        <v>16.470588235294</v>
       </c>
       <c r="L20" s="15">
-        <v>12.941176470588</v>
+        <v>13.793103448275</v>
       </c>
       <c r="M20" s="15">
-        <v>113.333333333333</v>
+        <v>115.217391304348</v>
       </c>
       <c r="N20" s="15">
-        <v>-90.606653620352</v>
+        <v>-90.934065934065</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D21" s="17">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E21" s="18">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F21" s="17">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G21" s="17">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="H21" s="18">
-        <v>-15.116279069767</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="I21" s="17">
-        <v>361</v>
+        <v>380</v>
       </c>
       <c r="J21" s="17">
-        <v>355</v>
+        <v>382</v>
       </c>
       <c r="K21" s="18">
-        <v>1.690140845070</v>
+        <v>-0.523560209424</v>
       </c>
       <c r="L21" s="18">
-        <v>-1.902173913043</v>
+        <v>-3.553299492385</v>
       </c>
       <c r="M21" s="18">
-        <v>20.333333333333</v>
+        <v>20.253164556962</v>
       </c>
       <c r="N21" s="18">
-        <v>-78.160919540229</v>
+        <v>-78.482446206115</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D24" s="14">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E24" s="15">
-        <v>-46.153846153846</v>
+        <v>0</v>
       </c>
       <c r="F24" s="14">
+        <v>38</v>
+      </c>
+      <c r="G24" s="14">
         <v>40</v>
       </c>
-      <c r="G24" s="14">
-        <v>44</v>
-      </c>
       <c r="H24" s="15">
-        <v>-9.090909090909</v>
+        <v>-5</v>
       </c>
       <c r="I24" s="14">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="J24" s="14">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="K24" s="15">
-        <v>-21.714285714285</v>
+        <v>-20.430107526881</v>
       </c>
       <c r="L24" s="15">
-        <v>-18.934911242603</v>
+        <v>-20.855614973262</v>
       </c>
       <c r="M24" s="15">
-        <v>-13.291139240506</v>
+        <v>-12.941176470588</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,31 +1306,31 @@
         <v>20</v>
       </c>
       <c r="D25" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E25" s="15">
         <v>-100</v>
       </c>
       <c r="F25" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G25" s="14">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H25" s="15">
-        <v>-71.428571428571</v>
+        <v>-91.666666666666</v>
       </c>
       <c r="I25" s="14">
         <v>11</v>
       </c>
       <c r="J25" s="14">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K25" s="15">
-        <v>-67.647058823529</v>
+        <v>-71.052631578947</v>
       </c>
       <c r="L25" s="15">
-        <v>-71.794871794871</v>
+        <v>-73.170731707317</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D26" s="14">
+        <v>3</v>
+      </c>
+      <c r="E26" s="15">
+        <v>-66.666666666666</v>
+      </c>
+      <c r="F26" s="14">
         <v>9</v>
       </c>
-      <c r="E26" s="15">
-        <v>-77.777777777777</v>
-      </c>
-      <c r="F26" s="14">
-        <v>12</v>
-      </c>
       <c r="G26" s="14">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H26" s="15">
-        <v>-36.842105263157</v>
+        <v>-47.058823529411</v>
       </c>
       <c r="I26" s="14">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J26" s="14">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="K26" s="15">
-        <v>-23.214285714285</v>
+        <v>-25.423728813559</v>
       </c>
       <c r="L26" s="15">
-        <v>-27.118644067796</v>
+        <v>-26.666666666666</v>
       </c>
       <c r="M26" s="15">
-        <v>-2.272727272727</v>
+        <v>-12</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1396,11 +1396,11 @@
       <c r="F27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G27" s="14">
-        <v>1</v>
-      </c>
-      <c r="H27" s="15">
-        <v>-100</v>
+      <c r="G27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I27" s="14">
         <v>2</v>
@@ -1435,25 +1435,25 @@
         <v>0</v>
       </c>
       <c r="F28" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G28" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H28" s="15">
         <v>0</v>
       </c>
       <c r="I28" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J28" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K28" s="15">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L28" s="15">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1551,17 +1551,17 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="14">
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G31" s="14">
         <v>1</v>
-      </c>
-      <c r="E31" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G31" s="14">
-        <v>2</v>
       </c>
       <c r="H31" s="15">
         <v>-100</v>
@@ -1576,7 +1576,7 @@
         <v>0</v>
       </c>
       <c r="L31" s="15">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1607,8 +1607,8 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="14">
-        <v>1</v>
+      <c r="C33" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-111pct.xlsx
+++ b/data/source/weekly/cs-en-us-111pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -863,11 +863,11 @@
       <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="14">
-        <v>1</v>
-      </c>
-      <c r="H14" s="15">
-        <v>-100</v>
+      <c r="G14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I14" s="13" t="s">
         <v>20</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>1</v>
-      </c>
-      <c r="D16" s="14">
-        <v>2</v>
-      </c>
-      <c r="E16" s="15">
-        <v>-50</v>
+        <v>3</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F16" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G16" s="14">
         <v>2</v>
       </c>
       <c r="H16" s="15">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="I16" s="14">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J16" s="14">
         <v>9</v>
       </c>
       <c r="K16" s="15">
-        <v>33.333333333333</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L16" s="15">
-        <v>-36.842105263157</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="M16" s="15">
-        <v>-53.846153846153</v>
+        <v>-46.428571428571</v>
       </c>
       <c r="N16" s="15">
-        <v>-90.322580645161</v>
+        <v>-88.461538461538</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,37 +978,37 @@
         <v>4</v>
       </c>
       <c r="D17" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E17" s="15">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="F17" s="14">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G17" s="14">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H17" s="15">
-        <v>-15.384615384615</v>
+        <v>50</v>
       </c>
       <c r="I17" s="14">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="J17" s="14">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K17" s="15">
-        <v>-34.090909090909</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="L17" s="15">
-        <v>3.571428571428</v>
+        <v>16.666666666666</v>
       </c>
       <c r="M17" s="15">
-        <v>38.095238095238</v>
+        <v>66.666666666666</v>
       </c>
       <c r="N17" s="15">
-        <v>-35.555555555555</v>
+        <v>-22.222222222222</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,37 +1019,37 @@
         <v>4</v>
       </c>
       <c r="D18" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E18" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F18" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G18" s="14">
         <v>21</v>
       </c>
       <c r="H18" s="15">
-        <v>-47.619047619047</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="I18" s="14">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="J18" s="14">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="K18" s="15">
-        <v>-42.268041237113</v>
+        <v>-41.747572815534</v>
       </c>
       <c r="L18" s="15">
-        <v>-35.632183908046</v>
+        <v>-32.584269662921</v>
       </c>
       <c r="M18" s="15">
-        <v>-35.632183908046</v>
+        <v>-34.065934065934</v>
       </c>
       <c r="N18" s="15">
-        <v>-83.183183183183</v>
+        <v>-83.002832861189</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D19" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E19" s="15">
-        <v>-25</v>
+        <v>-70</v>
       </c>
       <c r="F19" s="14">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G19" s="14">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H19" s="15">
-        <v>-14.705882352941</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="I19" s="14">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="J19" s="14">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="K19" s="15">
-        <v>27.972027972028</v>
+        <v>22.875816993464</v>
       </c>
       <c r="L19" s="15">
-        <v>7.647058823529</v>
+        <v>7.428571428571</v>
       </c>
       <c r="M19" s="15">
-        <v>36.567164179104</v>
+        <v>34.285714285714</v>
       </c>
       <c r="N19" s="15">
-        <v>10.240963855421</v>
+        <v>7.428571428571</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D20" s="14">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E20" s="15">
-        <v>-72.727272727272</v>
+        <v>-50</v>
       </c>
       <c r="F20" s="14">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="G20" s="14">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H20" s="15">
-        <v>-14.814814814814</v>
+        <v>-34.615384615384</v>
       </c>
       <c r="I20" s="14">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="J20" s="14">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="K20" s="15">
-        <v>16.470588235294</v>
+        <v>13.483146067415</v>
       </c>
       <c r="L20" s="15">
-        <v>13.793103448275</v>
+        <v>10.989010989011</v>
       </c>
       <c r="M20" s="15">
-        <v>115.217391304348</v>
+        <v>114.893617021277</v>
       </c>
       <c r="N20" s="15">
-        <v>-90.934065934065</v>
+        <v>-91.171328671328</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D21" s="17">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="E21" s="18">
-        <v>-33.333333333333</v>
+        <v>-23.809523809523</v>
       </c>
       <c r="F21" s="17">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="G21" s="17">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="H21" s="18">
-        <v>-21.428571428571</v>
+        <v>-13.043478260869</v>
       </c>
       <c r="I21" s="17">
-        <v>380</v>
+        <v>400</v>
       </c>
       <c r="J21" s="17">
-        <v>382</v>
+        <v>403</v>
       </c>
       <c r="K21" s="18">
-        <v>-0.523560209424</v>
+        <v>-0.744416873449</v>
       </c>
       <c r="L21" s="18">
-        <v>-3.553299492385</v>
+        <v>-2.200488997555</v>
       </c>
       <c r="M21" s="18">
-        <v>20.253164556962</v>
+        <v>21.580547112462</v>
       </c>
       <c r="N21" s="18">
-        <v>-78.482446206115</v>
+        <v>-78.413383702104</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D24" s="14">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E24" s="15">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F24" s="14">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G24" s="14">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="H24" s="15">
-        <v>-5</v>
+        <v>9.090909090909</v>
       </c>
       <c r="I24" s="14">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="J24" s="14">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="K24" s="15">
-        <v>-20.430107526881</v>
+        <v>-19.895287958115</v>
       </c>
       <c r="L24" s="15">
-        <v>-20.855614973262</v>
+        <v>-21.938775510204</v>
       </c>
       <c r="M24" s="15">
-        <v>-12.941176470588</v>
+        <v>-13.068181818181</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,7 +1306,7 @@
         <v>20</v>
       </c>
       <c r="D25" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E25" s="15">
         <v>-100</v>
@@ -1315,22 +1315,22 @@
         <v>1</v>
       </c>
       <c r="G25" s="14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H25" s="15">
-        <v>-91.666666666666</v>
+        <v>-90</v>
       </c>
       <c r="I25" s="14">
         <v>11</v>
       </c>
       <c r="J25" s="14">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K25" s="15">
-        <v>-71.052631578947</v>
+        <v>-71.794871794871</v>
       </c>
       <c r="L25" s="15">
-        <v>-73.170731707317</v>
+        <v>-74.418604651162</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D26" s="14">
         <v>3</v>
       </c>
       <c r="E26" s="15">
-        <v>-66.666666666666</v>
+        <v>166.666666666667</v>
       </c>
       <c r="F26" s="14">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G26" s="14">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H26" s="15">
-        <v>-47.058823529411</v>
+        <v>-30</v>
       </c>
       <c r="I26" s="14">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="J26" s="14">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K26" s="15">
-        <v>-25.423728813559</v>
+        <v>-14.516129032258</v>
       </c>
       <c r="L26" s="15">
-        <v>-26.666666666666</v>
+        <v>-20.895522388059</v>
       </c>
       <c r="M26" s="15">
-        <v>-12</v>
+        <v>0</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1425,14 +1425,14 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>1</v>
-      </c>
-      <c r="D28" s="14">
-        <v>1</v>
-      </c>
-      <c r="E28" s="15">
-        <v>0</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
         <v>2</v>
@@ -1478,11 +1478,11 @@
       <c r="F29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G29" s="14">
-        <v>1</v>
-      </c>
-      <c r="H29" s="15">
-        <v>-100</v>
+      <c r="G29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I29" s="13" t="s">
         <v>20</v>
@@ -1519,11 +1519,11 @@
       <c r="F30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G30" s="14">
-        <v>1</v>
-      </c>
-      <c r="H30" s="15">
-        <v>-100</v>
+      <c r="G30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I30" s="13" t="s">
         <v>20</v>
